--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="市場動向" sheetId="1" r:id="R863d578dd0fc45b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="數值明細" sheetId="2" r:id="Rfe11e92f299a42a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位說明" sheetId="3" r:id="R6e052e21b100487e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="市場動向" sheetId="1" r:id="R6b94f833ed9049e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="數值明細" sheetId="2" r:id="Ra0658e161b7e4912"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位說明" sheetId="3" r:id="Rd6776d5bdc7b4b11"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,7 +38,7 @@
       <x:name val="Noto Sans CJK TC"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,8 +50,13 @@
         <x:fgColor rgb="FF193D34"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="4">
     <x:border>
       <x:left/>
       <x:right/>
@@ -59,11 +64,40 @@
       <x:bottom/>
       <x:diagonal/>
     </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFDCE4DE"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFDCE4DE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFDCE4DE"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFDCE4DE"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -84,16 +118,46 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -127,7 +191,7 @@
     <x:tableColumn id="18" name="來源類型"/>
     <x:tableColumn id="19" name="來源連結"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -158,7 +222,7 @@
     <x:tableColumn id="21" name="對 AEIS 影響評估（分析）"/>
     <x:tableColumn id="22" name="來源連結"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -169,7 +233,7 @@
     <x:tableColumn id="1" name="欄位／方法"/>
     <x:tableColumn id="2" name="定義"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -452,541 +516,541 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A2" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="d">
+      <x:c r="A2" s="12" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="9" t="str">
         <x:v>2026-10-17:12</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="9" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="9" t="str">
         <x:v>AI 半導體；HBM；先進封裝；測試</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="9" t="str">
         <x:v>晶圓製造至封裝測試</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="9" t="str">
         <x:v>美光 AATT2 開幕，新增投資額未核實</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="H2" s="9" t="str">
         <x:v>公司描述先進封裝需求，未核實新增產量</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str">
+      <x:c r="I2" s="9" t="str">
         <x:v>美商在台廠房開幕，新增金額未披露</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="str">
+      <x:c r="J2" s="9" t="str">
         <x:v>本週追蹤：AI 晶片供給要同時看 CoWoS、HBM 與後段測試</x:v>
       </x:c>
-      <x:c r="K2" s="3" t="str">
+      <x:c r="K2" s="9" t="str">
         <x:v>台積電 10 月 15 日法說表示，5 倍光罩尺寸的 CoWoS 已量產；同日美光台中 AATT2 先進封裝測試廠開幕，支援 HBM。這兩項是本週進展，今日整合追蹤，並無新增產能數字。</x:v>
       </x:c>
-      <x:c r="L2" s="3" t="str">
+      <x:c r="L2" s="9" t="str">
         <x:v>半導體設備精密電源，間接需求</x:v>
       </x:c>
-      <x:c r="M2" s="3" t="str">
+      <x:c r="M2" s="9" t="str">
         <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
       </x:c>
-      <x:c r="N2" s="3" t="str">
+      <x:c r="N2" s="9" t="str">
         <x:v>近期認證與中期設備拉貨</x:v>
       </x:c>
-      <x:c r="O2" s="3" t="str">
+      <x:c r="O2" s="9" t="str">
         <x:v>確認設備客戶認證及備料節奏</x:v>
       </x:c>
-      <x:c r="P2" s="3" t="str">
+      <x:c r="P2" s="9" t="str">
         <x:v>實際產能、良率、利用率與設備訂單</x:v>
       </x:c>
-      <x:c r="Q2" s="3" t="str">
+      <x:c r="Q2" s="9" t="str">
         <x:v>高</x:v>
       </x:c>
-      <x:c r="R2" s="3" t="str">
+      <x:c r="R2" s="9" t="str">
         <x:v>First-hand</x:v>
       </x:c>
-      <x:c r="S2" s="3" t="e">
+      <x:c r="S2" s="9" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-12","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-12, friendlyName=完整來源與日報</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A3" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="d">
+      <x:c r="A3" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B3" s="13" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="C3" s="10" t="str">
         <x:v>2026-10-17:13</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="E3" s="10" t="str">
         <x:v>AI 資料中心；伺服器；電源；液冷</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>ODM 整機櫃至機房交付</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
+      <x:c r="G3" s="10" t="str">
         <x:v>產品展示，未披露新增資本支出</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="str">
+      <x:c r="H3" s="10" t="str">
         <x:v>800 VDC 與液冷方案增加，出貨量未核實</x:v>
       </x:c>
-      <x:c r="I3" s="3" t="str">
+      <x:c r="I3" s="10" t="str">
         <x:v>未披露外商投資金額</x:v>
       </x:c>
-      <x:c r="J3" s="3" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>OCP 台廠展示整機櫃、800 VDC 電源與液冷，量產驗收成為下一關</x:v>
       </x:c>
-      <x:c r="K3" s="3" t="str">
+      <x:c r="K3" s="10" t="str">
         <x:v>中央社 10 月 17 日整理 10 月 12 至 15 日 OCP 展會：緯穎、華碩與勤誠等展示下一代伺服器或機櫃，台達電、光寶與康舒展示高壓直流電源及相關方案。台達電 10 月 15 日公司稿列出 800 VDC 電源櫃、備援與液冷產品，展示規格仍需與量產部署分開。</x:v>
       </x:c>
-      <x:c r="L3" s="3" t="str">
+      <x:c r="L3" s="10" t="str">
         <x:v>資料中心電源直接相關，未證實 AEIS 新訂單</x:v>
       </x:c>
-      <x:c r="M3" s="3" t="str">
+      <x:c r="M3" s="10" t="str">
         <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
       </x:c>
-      <x:c r="N3" s="3" t="str">
+      <x:c r="N3" s="10" t="str">
         <x:v>依客戶認證及量產時程</x:v>
       </x:c>
-      <x:c r="O3" s="3" t="str">
+      <x:c r="O3" s="10" t="str">
         <x:v>比較系統整合、效率與服務條件</x:v>
       </x:c>
-      <x:c r="P3" s="3" t="str">
+      <x:c r="P3" s="10" t="str">
         <x:v>認證、量產訂單與每櫃電源價值</x:v>
       </x:c>
-      <x:c r="Q3" s="3" t="str">
+      <x:c r="Q3" s="10" t="str">
         <x:v>高</x:v>
       </x:c>
-      <x:c r="R3" s="3" t="str">
+      <x:c r="R3" s="10" t="str">
         <x:v>Second-hand; First-hand</x:v>
       </x:c>
-      <x:c r="S3" s="3" t="e">
+      <x:c r="S3" s="10" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-13","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-13, friendlyName=完整來源與日報</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A4" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="A4" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B4" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
         <x:v>2026-10-17:14</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>台灣</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>玻璃基板；光通訊；先進封裝</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>材料零組件及製程設備</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>轉型目標，資本支出未披露</x:v>
       </x:c>
-      <x:c r="H4" s="3" t="str">
+      <x:c r="H4" s="10" t="str">
         <x:v>封裝及光通訊需求尚待認證</x:v>
       </x:c>
-      <x:c r="I4" s="3" t="str">
+      <x:c r="I4" s="10" t="str">
         <x:v>與康寧合作屬技術合作，未核實投資流入</x:v>
       </x:c>
-      <x:c r="J4" s="3" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>友達布局玻璃基板與光通訊零組件，2030 年純面板占比目標為 30%</x:v>
       </x:c>
-      <x:c r="K4" s="3" t="str">
+      <x:c r="K4" s="10" t="str">
         <x:v>友達董事長彭双浪 10 月 17 日表示，公司在先進封裝將扮演零組件供應者，運用玻璃與 TGV 技術；與康寧合作的技術已有低軌衛星天線應用。MicroLED 光通訊與 CPO 的量產時間估計仍為兩至三年，屬公司展望。</x:v>
       </x:c>
-      <x:c r="L4" s="3" t="str">
+      <x:c r="L4" s="10" t="str">
         <x:v>新材料設備電源的潛在需求</x:v>
       </x:c>
-      <x:c r="M4" s="3" t="str">
+      <x:c r="M4" s="10" t="str">
         <x:v>分析：先辨識新材料製程使用哪些設備、是否增加電源控制要求，再決定工程投入。零組件轉型可能形成設備需求，現階段未有可量化的 AEIS 訂單或資本支出影響。</x:v>
       </x:c>
-      <x:c r="N4" s="3" t="str">
+      <x:c r="N4" s="10" t="str">
         <x:v>光通訊量產展望兩至三年，屬公司估計</x:v>
       </x:c>
-      <x:c r="O4" s="3" t="str">
+      <x:c r="O4" s="10" t="str">
         <x:v>先確認製程與可服務設備</x:v>
       </x:c>
-      <x:c r="P4" s="3" t="str">
+      <x:c r="P4" s="10" t="str">
         <x:v>客戶認證、量產良率與新業務收入</x:v>
       </x:c>
-      <x:c r="Q4" s="3" t="str">
+      <x:c r="Q4" s="10" t="str">
         <x:v>中</x:v>
       </x:c>
-      <x:c r="R4" s="3" t="str">
+      <x:c r="R4" s="10" t="str">
         <x:v>Second-hand</x:v>
       </x:c>
-      <x:c r="S4" s="3" t="e">
+      <x:c r="S4" s="10" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-14","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-14, friendlyName=完整來源與日報</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A5" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="d">
+      <x:c r="A5" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>2026-10-17:15</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="str">
+      <x:c r="D5" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="str">
+      <x:c r="E5" s="10" t="str">
         <x:v>終端 AI；PC；IC 設計；封裝</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="str">
+      <x:c r="F5" s="10" t="str">
         <x:v>設計至品牌 PC 與企業用戶</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="str">
+      <x:c r="G5" s="10" t="str">
         <x:v>新品推出，未披露新廠投資</x:v>
       </x:c>
-      <x:c r="H5" s="3" t="str">
+      <x:c r="H5" s="10" t="str">
         <x:v>公司預期本地 AI 需求，尚無售出量</x:v>
       </x:c>
-      <x:c r="I5" s="3" t="str">
+      <x:c r="I5" s="10" t="str">
         <x:v>未披露</x:v>
       </x:c>
-      <x:c r="J5" s="3" t="str">
+      <x:c r="J5" s="10" t="str">
         <x:v>RTX Spark 電腦 10 月 16 日上市，台灣設計、封裝與品牌串接終端 AI</x:v>
       </x:c>
-      <x:c r="K5" s="3" t="str">
+      <x:c r="K5" s="10" t="str">
         <x:v>NVIDIA 10 月 16 日宣布 RTX Spark Windows 電腦上市，品牌包括華碩、微星及多家國際 PC 廠，採 Grace CPU 與 Blackwell GPU。公司主管向中央社說明聯發科參與 CPU 設計，並使用 CoWoS 封裝；需求與產能判斷仍屬公司說法。</x:v>
       </x:c>
-      <x:c r="L5" s="3" t="str">
+      <x:c r="L5" s="10" t="str">
         <x:v>PC 電源與製程電源機會需分開</x:v>
       </x:c>
-      <x:c r="M5" s="3" t="str">
+      <x:c r="M5" s="10" t="str">
         <x:v>分析：分別追蹤前段設備電源、封裝設備及 PC 系統電源的可服務範圍。新品上市尚不足以調高供應量，應等待通路售出、企業導入、退貨率與平台毛利。</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="str">
+      <x:c r="N5" s="10" t="str">
         <x:v>新品上市後數季</x:v>
       </x:c>
-      <x:c r="O5" s="3" t="str">
+      <x:c r="O5" s="10" t="str">
         <x:v>等待售出與企業導入，再調整供應</x:v>
       </x:c>
-      <x:c r="P5" s="3" t="str">
+      <x:c r="P5" s="10" t="str">
         <x:v>出貨、使用率、能耗與退貨率</x:v>
       </x:c>
-      <x:c r="Q5" s="3" t="str">
+      <x:c r="Q5" s="10" t="str">
         <x:v>高</x:v>
       </x:c>
-      <x:c r="R5" s="3" t="str">
+      <x:c r="R5" s="10" t="str">
         <x:v>First-hand; Second-hand</x:v>
       </x:c>
-      <x:c r="S5" s="3" t="e">
+      <x:c r="S5" s="10" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-15","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-15, friendlyName=完整來源與日報</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A6" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="d">
+      <x:c r="A6" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="str">
+      <x:c r="C6" s="10" t="str">
         <x:v>2026-10-17:4</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="str">
+      <x:c r="D6" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="str">
+      <x:c r="E6" s="10" t="str">
         <x:v>海外工業園區；電子供應鏈</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="str">
+      <x:c r="F6" s="10" t="str">
         <x:v>零組件至在地工廠</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="str">
+      <x:c r="G6" s="10" t="str">
         <x:v>每座 20 億至 40 億美元估算，未承諾</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="str">
+      <x:c r="H6" s="10" t="str">
         <x:v>在地供應鏈規劃，租用率未公布</x:v>
       </x:c>
-      <x:c r="I6" s="3" t="str">
+      <x:c r="I6" s="10" t="str">
         <x:v>私人籌資規劃，尚非實際投資流量</x:v>
       </x:c>
-      <x:c r="J6" s="3" t="str">
+      <x:c r="J6" s="10" t="str">
         <x:v>經濟部說明赴美園區由業者籌資，每座估 20 億至 40 億美元</x:v>
       </x:c>
-      <x:c r="K6" s="3" t="str">
+      <x:c r="K6" s="10" t="str">
         <x:v>經濟部 10 月 16 日向中央社說明，將與電電公會推動海外產業園區，採業者出資、政府協助模式。龔明鑫專訪提及由德州起步、規劃不只一座；單一園區 20 億至 40 億美元是估算，土地取得細節尚未對外確認。</x:v>
       </x:c>
-      <x:c r="L6" s="3" t="str">
+      <x:c r="L6" s="10" t="str">
         <x:v>在地服務、庫存與製造成本</x:v>
       </x:c>
-      <x:c r="M6" s="3" t="str">
+      <x:c r="M6" s="10" t="str">
         <x:v>大型客戶在美國蓋廠，只完成供應鏈在地化的一部分。對中小供應商，關鍵是園區能否提供穩定訂單、共用設施與可負擔的資金，而不只是一塊海外土地。</x:v>
       </x:c>
-      <x:c r="N6" s="3" t="str">
+      <x:c r="N6" s="10" t="str">
         <x:v>用地及融資確定後</x:v>
       </x:c>
-      <x:c r="O6" s="3" t="str">
+      <x:c r="O6" s="10" t="str">
         <x:v>以已簽需求檢查布局</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="str">
+      <x:c r="P6" s="10" t="str">
         <x:v>融資、土地、入駐名單與動工</x:v>
       </x:c>
-      <x:c r="Q6" s="3" t="str">
+      <x:c r="Q6" s="10" t="str">
         <x:v>中</x:v>
       </x:c>
-      <x:c r="R6" s="3" t="str">
+      <x:c r="R6" s="10" t="str">
         <x:v>Second-hand</x:v>
       </x:c>
-      <x:c r="S6" s="3" t="e">
+      <x:c r="S6" s="10" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-4","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-4, friendlyName=完整來源與日報</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A7" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B7" s="8" t="d">
+      <x:c r="A7" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>2026-10-17:11</x:v>
       </x:c>
-      <x:c r="D7" s="3" t="str">
+      <x:c r="D7" s="10" t="str">
         <x:v>台灣</x:v>
       </x:c>
-      <x:c r="E7" s="3" t="str">
+      <x:c r="E7" s="10" t="str">
         <x:v>總體經濟；AI 投資</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="str">
+      <x:c r="F7" s="10" t="str">
         <x:v>需求與區域投資背景</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="str">
+      <x:c r="G7" s="10" t="str">
         <x:v>中經院投資展望，屬預測</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="str">
+      <x:c r="H7" s="10" t="str">
         <x:v>2026 年 GDP 成長預測 12.16%</x:v>
       </x:c>
-      <x:c r="I7" s="3" t="str">
+      <x:c r="I7" s="10" t="str">
         <x:v>未提供本期 FDI 數據</x:v>
       </x:c>
-      <x:c r="J7" s="3" t="str">
+      <x:c r="J7" s="10" t="str">
         <x:v>中經院上修台灣全年成長預測至 12.16%，需分開看實績與展望</x:v>
       </x:c>
-      <x:c r="K7" s="3" t="str">
+      <x:c r="K7" s="10" t="str">
         <x:v>中經院 10 月 16 日公布第四季預測，把 2026 年經濟成長率由 7 月的 10.35% 上修至 12.16%，提高 1.81 個百分點。預估內需貢獻 6.63 個百分點、國外淨需求貢獻 5.53 個百分點；全年數字仍是預測。</x:v>
       </x:c>
-      <x:c r="L7" s="3" t="str">
+      <x:c r="L7" s="10" t="str">
         <x:v>客戶資本支出與區域服務規劃</x:v>
       </x:c>
-      <x:c r="M7" s="3" t="str">
+      <x:c r="M7" s="10" t="str">
         <x:v>這份預測的重點是 AI 硬體需求如何傳到投資與消費。分析時仍要分清：少數出口產業的強勁成長、整體 GDP，以及每個人的收入感受，三者不會等比例變動。</x:v>
       </x:c>
-      <x:c r="N7" s="3" t="str">
+      <x:c r="N7" s="10" t="str">
         <x:v>2026 年全年預測</x:v>
       </x:c>
-      <x:c r="O7" s="3" t="str">
+      <x:c r="O7" s="10" t="str">
         <x:v>用設備客戶訂單驗證總體展望</x:v>
       </x:c>
-      <x:c r="P7" s="3" t="str">
+      <x:c r="P7" s="10" t="str">
         <x:v>GDP 實績、民間投資與客戶拉貨</x:v>
       </x:c>
-      <x:c r="Q7" s="3" t="str">
+      <x:c r="Q7" s="10" t="str">
         <x:v>高</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="str">
+      <x:c r="R7" s="10" t="str">
         <x:v>First-hand; Second-hand</x:v>
       </x:c>
-      <x:c r="S7" s="3" t="e">
+      <x:c r="S7" s="10" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-11","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-11, friendlyName=完整來源與日報</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A8" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B8" s="8" t="d">
+      <x:c r="A8" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="str">
+      <x:c r="C8" s="10" t="str">
         <x:v>2026-10-17:18</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="str">
+      <x:c r="D8" s="10" t="str">
         <x:v>越南</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="str">
+      <x:c r="E8" s="10" t="str">
         <x:v>AI 資料中心；電源；能源</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="str">
+      <x:c r="F8" s="10" t="str">
         <x:v>機房建設與營運電力</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="str">
+      <x:c r="G8" s="10" t="str">
         <x:v>21 億美元既有計畫，新增投資未核實</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="str">
+      <x:c r="H8" s="10" t="str">
         <x:v>電價爭點可能影響進度，量化需求未知</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="str">
+      <x:c r="I8" s="10" t="str">
         <x:v>AIC 與 KBC 既有計畫，非新流入</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="str">
+      <x:c r="J8" s="10" t="str">
         <x:v>胡志明市要求釐清 AI 資料中心電價，投資模型面臨費率認定</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="str">
+      <x:c r="K8" s="10" t="str">
         <x:v>TNGlobal 10 月 16 日報導，胡志明市工業區管理機關在 10 月 15 日經濟會議要求統一 AI 資料中心電價指引。所涉 AIC 與 KBC 計畫早於 3 月公布，總規劃金額 21 億美元；本次新增進展是電價問題，並非新宣布投資。</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="str">
+      <x:c r="L8" s="10" t="str">
         <x:v>資料中心電源，部署時點風險</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="str">
+      <x:c r="M8" s="10" t="str">
         <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 AEIS 收入或投資回收。</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="str">
+      <x:c r="N8" s="10" t="str">
         <x:v>待費率分類與電力合約</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="str">
+      <x:c r="O8" s="10" t="str">
         <x:v>確認電力條件再排工程及交貨</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="str">
+      <x:c r="P8" s="10" t="str">
         <x:v>正式費率、融資與上線</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="str">
+      <x:c r="Q8" s="10" t="str">
         <x:v>中</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="str">
+      <x:c r="R8" s="10" t="str">
         <x:v>Second-hand</x:v>
       </x:c>
-      <x:c r="S8" s="3" t="e">
+      <x:c r="S8" s="10" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-18","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-18, friendlyName=完整來源與日報</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A9" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B9" s="8" t="d">
+      <x:c r="A9" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>2026-10-17:19</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="str">
+      <x:c r="D9" s="10" t="str">
         <x:v>馬來西亞；台灣</x:v>
       </x:c>
-      <x:c r="E9" s="3" t="str">
+      <x:c r="E9" s="10" t="str">
         <x:v>半導體；後段封測；設備服務</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="str">
+      <x:c r="F9" s="10" t="str">
         <x:v>設計至封測及現場工程</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="str">
+      <x:c r="G9" s="10" t="str">
         <x:v>人才與園區布局，非已確認新廠投資</x:v>
       </x:c>
-      <x:c r="H9" s="3" t="str">
+      <x:c r="H9" s="10" t="str">
         <x:v>逾 1,500 職缺，非實際聘用</x:v>
       </x:c>
-      <x:c r="I9" s="3" t="str">
+      <x:c r="I9" s="10" t="str">
         <x:v>未提供新增 FDI 流量</x:v>
       </x:c>
-      <x:c r="J9" s="3" t="str">
+      <x:c r="J9" s="10" t="str">
         <x:v>馬來西亞半導體招募涵蓋製程、設備與廠務，人才連結台灣供應鏈</x:v>
       </x:c>
-      <x:c r="K9" s="3" t="str">
+      <x:c r="K9" s="10" t="str">
         <x:v>中央社 10 月 16 日報導，雪蘭莪 10 月 14 至 17 日半導體招募活動提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備及廠務。官員表示兩座 IC 設計園區有 20 家公司、409 名工程師，並將雪蘭莪設計與檳城製造、組裝測試視為互補。</x:v>
       </x:c>
-      <x:c r="L9" s="3" t="str">
+      <x:c r="L9" s="10" t="str">
         <x:v>區域服務與工程人才，間接相關</x:v>
       </x:c>
-      <x:c r="M9" s="3" t="str">
+      <x:c r="M9" s="10" t="str">
         <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 AEIS 合作、客戶採購或新的工廠投資。</x:v>
       </x:c>
-      <x:c r="N9" s="3" t="str">
+      <x:c r="N9" s="10" t="str">
         <x:v>當期招募與後續認證</x:v>
       </x:c>
-      <x:c r="O9" s="3" t="str">
+      <x:c r="O9" s="10" t="str">
         <x:v>檢查客戶密度、人才與維修週轉</x:v>
       </x:c>
-      <x:c r="P9" s="3" t="str">
+      <x:c r="P9" s="10" t="str">
         <x:v>聘用、留任與客戶設備認證</x:v>
       </x:c>
-      <x:c r="Q9" s="3" t="str">
+      <x:c r="Q9" s="10" t="str">
         <x:v>中</x:v>
       </x:c>
-      <x:c r="R9" s="3" t="str">
+      <x:c r="R9" s="10" t="str">
         <x:v>Second-hand</x:v>
       </x:c>
-      <x:c r="S9" s="3" t="e">
+      <x:c r="S9" s="10" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-19","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-19, friendlyName=完整來源與日報</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A10" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B10" s="8" t="d">
+      <x:c r="A10" s="14" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C10" s="3" t="str">
+      <x:c r="C10" s="11" t="str">
         <x:v>2026-10-17:20</x:v>
       </x:c>
-      <x:c r="D10" s="3" t="str">
+      <x:c r="D10" s="11" t="str">
         <x:v>越南；新加坡</x:v>
       </x:c>
-      <x:c r="E10" s="3" t="str">
+      <x:c r="E10" s="11" t="str">
         <x:v>製造業；外商投資；工業電源</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="str">
+      <x:c r="F10" s="11" t="str">
         <x:v>資金註冊至工廠落地</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="str">
+      <x:c r="G10" s="11" t="str">
         <x:v>總註冊外資 503.6 億美元</x:v>
       </x:c>
-      <x:c r="H10" s="3" t="str">
+      <x:c r="H10" s="11" t="str">
         <x:v>工廠設備需求尚須分項驗證</x:v>
       </x:c>
-      <x:c r="I10" s="3" t="str">
+      <x:c r="I10" s="11" t="str">
         <x:v>FDI 實現額估 210.7 億美元，YoY 12.1%</x:v>
       </x:c>
-      <x:c r="J10" s="3" t="str">
+      <x:c r="J10" s="11" t="str">
         <x:v>區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開</x:v>
       </x:c>
-      <x:c r="K10" s="3" t="str">
+      <x:c r="K10" s="11" t="str">
         <x:v>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。</x:v>
       </x:c>
-      <x:c r="L10" s="3" t="str">
+      <x:c r="L10" s="11" t="str">
         <x:v>在地工業電源與服務的背景指標</x:v>
       </x:c>
-      <x:c r="M10" s="3" t="str">
+      <x:c r="M10" s="11" t="str">
         <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 AEIS 的成長率。</x:v>
       </x:c>
-      <x:c r="N10" s="3" t="str">
+      <x:c r="N10" s="11" t="str">
         <x:v>截至 2026 年 9 月的區域背景</x:v>
       </x:c>
-      <x:c r="O10" s="3" t="str">
+      <x:c r="O10" s="11" t="str">
         <x:v>對到具名廠房與設備採購</x:v>
       </x:c>
-      <x:c r="P10" s="3" t="str">
+      <x:c r="P10" s="11" t="str">
         <x:v>製造業分項、電網接入與驗收</x:v>
       </x:c>
-      <x:c r="Q10" s="3" t="str">
+      <x:c r="Q10" s="11" t="str">
         <x:v>高</x:v>
       </x:c>
-      <x:c r="R10" s="3" t="str">
+      <x:c r="R10" s="11" t="str">
         <x:v>First-hand; Second-hand</x:v>
       </x:c>
-      <x:c r="S10" s="3" t="e">
+      <x:c r="S10" s="11" t="e">
         <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-20","完整來源與日報")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-20, friendlyName=完整來源與日報</x:v>
       </x:c>
@@ -994,7 +1058,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R182c7a99fc8a4b2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06561fd696054592"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1099,959 +1163,959 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="72" hidden="0" customHeight="1">
-      <x:c r="A2" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="d">
+      <x:c r="A2" s="12" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="9" t="str">
         <x:v>2026-10-17:12</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="9" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="9" t="str">
         <x:v>AI 半導體；HBM；先進封裝；測試</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="9" t="str">
         <x:v>新台幣營收（約）</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="9" t="str">
         <x:v>公司實績</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="H2" s="9" t="str">
         <x:v>2026 Q3</x:v>
       </x:c>
-      <x:c r="I2" s="9" t="n">
+      <x:c r="I2" s="15" t="n">
         <x:v>1494</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="str">
+      <x:c r="J2" s="9" t="str">
         <x:v>NTD billion</x:v>
       </x:c>
-      <x:c r="K2" s="3" t="str">
+      <x:c r="K2" s="9" t="str">
         <x:v>2025 Q3</x:v>
       </x:c>
-      <x:c r="L2" s="9"/>
-      <x:c r="M2" s="3" t="str">
+      <x:c r="L2" s="15"/>
+      <x:c r="M2" s="9" t="str">
         <x:v>YoY</x:v>
       </x:c>
-      <x:c r="N2" s="10" t="n">
+      <x:c r="N2" s="16" t="n">
         <x:v>0.509</x:v>
       </x:c>
-      <x:c r="O2" s="10"/>
-      <x:c r="P2" s="9"/>
-      <x:c r="Q2" s="9"/>
-      <x:c r="R2" s="10"/>
-      <x:c r="S2" s="3" t="str">
+      <x:c r="O2" s="16"/>
+      <x:c r="P2" s="15"/>
+      <x:c r="Q2" s="15"/>
+      <x:c r="R2" s="16"/>
+      <x:c r="S2" s="9" t="str">
         <x:v>本期值及公布增幅已核對；本表未收錄可比基期</x:v>
       </x:c>
-      <x:c r="T2" s="3" t="str">
+      <x:c r="T2" s="9" t="str">
         <x:v>TSMC</x:v>
       </x:c>
-      <x:c r="U2" s="3" t="str">
+      <x:c r="U2" s="9" t="str">
         <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
       </x:c>
-      <x:c r="V2" s="3" t="e">
+      <x:c r="V2" s="9" t="e">
         <x:f>HYPERLINK("https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf","https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf, friendlyName=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="72" hidden="0" customHeight="1">
-      <x:c r="A3" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="d">
+      <x:c r="A3" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B3" s="13" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="C3" s="10" t="str">
         <x:v>2026-10-17:12</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="E3" s="10" t="str">
         <x:v>AI 半導體；HBM；先進封裝；測試</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>稅後淨利</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
+      <x:c r="G3" s="10" t="str">
         <x:v>公司實績</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="str">
+      <x:c r="H3" s="10" t="str">
         <x:v>2026 Q3</x:v>
       </x:c>
-      <x:c r="I3" s="9" t="n">
+      <x:c r="I3" s="17" t="n">
         <x:v>763.06</x:v>
       </x:c>
-      <x:c r="J3" s="3" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>NTD billion</x:v>
       </x:c>
-      <x:c r="K3" s="3" t="str">
+      <x:c r="K3" s="10" t="str">
         <x:v>2025 Q3</x:v>
       </x:c>
-      <x:c r="L3" s="9"/>
-      <x:c r="M3" s="3" t="str">
+      <x:c r="L3" s="17"/>
+      <x:c r="M3" s="10" t="str">
         <x:v>YoY</x:v>
       </x:c>
-      <x:c r="N3" s="10" t="n">
+      <x:c r="N3" s="18" t="n">
         <x:v>0.687</x:v>
       </x:c>
-      <x:c r="O3" s="10"/>
-      <x:c r="P3" s="9"/>
-      <x:c r="Q3" s="9"/>
-      <x:c r="R3" s="10"/>
-      <x:c r="S3" s="3" t="str">
+      <x:c r="O3" s="18"/>
+      <x:c r="P3" s="17"/>
+      <x:c r="Q3" s="17"/>
+      <x:c r="R3" s="18"/>
+      <x:c r="S3" s="10" t="str">
         <x:v>本期值及公布增幅已核對；本表未收錄可比基期</x:v>
       </x:c>
-      <x:c r="T3" s="3" t="str">
+      <x:c r="T3" s="10" t="str">
         <x:v>TSMC</x:v>
       </x:c>
-      <x:c r="U3" s="3" t="str">
+      <x:c r="U3" s="10" t="str">
         <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
       </x:c>
-      <x:c r="V3" s="3" t="e">
+      <x:c r="V3" s="10" t="e">
         <x:f>HYPERLINK("https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf","https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf, friendlyName=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="72" hidden="0" customHeight="1">
-      <x:c r="A4" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="d">
+      <x:c r="A4" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B4" s="13" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>2026-10-17:12</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>AI 半導體；HBM；先進封裝；測試</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>美元營收</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>公司實績</x:v>
       </x:c>
-      <x:c r="H4" s="3" t="str">
+      <x:c r="H4" s="10" t="str">
         <x:v>2026 Q3</x:v>
       </x:c>
-      <x:c r="I4" s="9" t="n">
+      <x:c r="I4" s="17" t="n">
         <x:v>46.72</x:v>
       </x:c>
-      <x:c r="J4" s="3" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>USD billion</x:v>
       </x:c>
-      <x:c r="K4" s="3" t="str"/>
-      <x:c r="L4" s="9"/>
-      <x:c r="M4" s="3" t="str">
+      <x:c r="K4" s="10" t="str"/>
+      <x:c r="L4" s="17"/>
+      <x:c r="M4" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N4" s="10"/>
-      <x:c r="O4" s="10"/>
-      <x:c r="P4" s="9"/>
-      <x:c r="Q4" s="9"/>
-      <x:c r="R4" s="10"/>
-      <x:c r="S4" s="3" t="str">
+      <x:c r="N4" s="18"/>
+      <x:c r="O4" s="18"/>
+      <x:c r="P4" s="17"/>
+      <x:c r="Q4" s="17"/>
+      <x:c r="R4" s="18"/>
+      <x:c r="S4" s="10" t="str">
         <x:v>本期值及公布增幅已核對；本表未收錄可比基期</x:v>
       </x:c>
-      <x:c r="T4" s="3" t="str">
+      <x:c r="T4" s="10" t="str">
         <x:v>TSMC</x:v>
       </x:c>
-      <x:c r="U4" s="3" t="str">
+      <x:c r="U4" s="10" t="str">
         <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
       </x:c>
-      <x:c r="V4" s="3" t="e">
+      <x:c r="V4" s="10" t="e">
         <x:f>HYPERLINK("https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf","https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf, friendlyName=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" hidden="0" customHeight="1">
-      <x:c r="A5" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="d">
+      <x:c r="A5" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>2026-10-17:12</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="str">
+      <x:c r="D5" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="str">
+      <x:c r="E5" s="10" t="str">
         <x:v>AI 半導體；HBM；先進封裝；測試</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="str">
+      <x:c r="F5" s="10" t="str">
         <x:v>毛利率</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="str">
+      <x:c r="G5" s="10" t="str">
         <x:v>公司實績</x:v>
       </x:c>
-      <x:c r="H5" s="3" t="str">
+      <x:c r="H5" s="10" t="str">
         <x:v>2026 Q3</x:v>
       </x:c>
-      <x:c r="I5" s="11" t="n">
+      <x:c r="I5" s="19" t="n">
         <x:v>0.664</x:v>
       </x:c>
-      <x:c r="J5" s="3" t="str">
+      <x:c r="J5" s="10" t="str">
         <x:v>%</x:v>
       </x:c>
-      <x:c r="K5" s="3" t="str"/>
-      <x:c r="L5" s="11"/>
-      <x:c r="M5" s="3" t="str">
+      <x:c r="K5" s="10" t="str"/>
+      <x:c r="L5" s="19"/>
+      <x:c r="M5" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N5" s="10"/>
-      <x:c r="O5" s="10"/>
-      <x:c r="P5" s="9"/>
-      <x:c r="Q5" s="9"/>
-      <x:c r="R5" s="10"/>
-      <x:c r="S5" s="3" t="str">
+      <x:c r="N5" s="18"/>
+      <x:c r="O5" s="18"/>
+      <x:c r="P5" s="17"/>
+      <x:c r="Q5" s="17"/>
+      <x:c r="R5" s="18"/>
+      <x:c r="S5" s="10" t="str">
         <x:v>本期值及公布增幅已核對；本表未收錄可比基期</x:v>
       </x:c>
-      <x:c r="T5" s="3" t="str">
+      <x:c r="T5" s="10" t="str">
         <x:v>TSMC</x:v>
       </x:c>
-      <x:c r="U5" s="3" t="str">
+      <x:c r="U5" s="10" t="str">
         <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
       </x:c>
-      <x:c r="V5" s="3" t="e">
+      <x:c r="V5" s="10" t="e">
         <x:f>HYPERLINK("https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf","https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf, friendlyName=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="100.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A6" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="d">
+      <x:c r="A6" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="str">
+      <x:c r="C6" s="10" t="str">
         <x:v>2026-10-17:13</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="str">
+      <x:c r="D6" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="str">
+      <x:c r="E6" s="10" t="str">
         <x:v>AI 資料中心；伺服器；電源；液冷</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="str">
+      <x:c r="F6" s="10" t="str">
         <x:v>電源櫃額定能力</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="str">
+      <x:c r="G6" s="10" t="str">
         <x:v>產品規格</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="str">
+      <x:c r="H6" s="10" t="str">
         <x:v>OCP 2026 展示</x:v>
       </x:c>
-      <x:c r="I6" s="9" t="n">
+      <x:c r="I6" s="17" t="n">
         <x:v>660</x:v>
       </x:c>
-      <x:c r="J6" s="3" t="str">
+      <x:c r="J6" s="10" t="str">
         <x:v>kW</x:v>
       </x:c>
-      <x:c r="K6" s="3" t="str"/>
-      <x:c r="L6" s="9"/>
-      <x:c r="M6" s="3" t="str">
+      <x:c r="K6" s="10" t="str"/>
+      <x:c r="L6" s="17"/>
+      <x:c r="M6" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N6" s="10"/>
-      <x:c r="O6" s="10"/>
-      <x:c r="P6" s="9"/>
-      <x:c r="Q6" s="9"/>
-      <x:c r="R6" s="10"/>
-      <x:c r="S6" s="3" t="str">
+      <x:c r="N6" s="18"/>
+      <x:c r="O6" s="18"/>
+      <x:c r="P6" s="17"/>
+      <x:c r="Q6" s="17"/>
+      <x:c r="R6" s="18"/>
+      <x:c r="S6" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T6" s="3" t="str">
+      <x:c r="T6" s="10" t="str">
         <x:v>Delta</x:v>
       </x:c>
-      <x:c r="U6" s="3" t="str">
+      <x:c r="U6" s="10" t="str">
         <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
       </x:c>
-      <x:c r="V6" s="3" t="e">
+      <x:c r="V6" s="10" t="e">
         <x:f>HYPERLINK("https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html","https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html, friendlyName=https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="100.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A7" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B7" s="8" t="d">
+      <x:c r="A7" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>2026-10-17:13</x:v>
       </x:c>
-      <x:c r="D7" s="3" t="str">
+      <x:c r="D7" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E7" s="3" t="str">
+      <x:c r="E7" s="10" t="str">
         <x:v>AI 資料中心；伺服器；電源；液冷</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="str">
+      <x:c r="F7" s="10" t="str">
         <x:v>備援額定能力</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="str">
+      <x:c r="G7" s="10" t="str">
         <x:v>產品規格</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="str">
+      <x:c r="H7" s="10" t="str">
         <x:v>OCP 2026 展示</x:v>
       </x:c>
-      <x:c r="I7" s="9" t="n">
+      <x:c r="I7" s="17" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="J7" s="3" t="str">
+      <x:c r="J7" s="10" t="str">
         <x:v>kW</x:v>
       </x:c>
-      <x:c r="K7" s="3" t="str"/>
-      <x:c r="L7" s="9"/>
-      <x:c r="M7" s="3" t="str">
+      <x:c r="K7" s="10" t="str"/>
+      <x:c r="L7" s="17"/>
+      <x:c r="M7" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N7" s="10"/>
-      <x:c r="O7" s="10"/>
-      <x:c r="P7" s="9"/>
-      <x:c r="Q7" s="9"/>
-      <x:c r="R7" s="10"/>
-      <x:c r="S7" s="3" t="str">
+      <x:c r="N7" s="18"/>
+      <x:c r="O7" s="18"/>
+      <x:c r="P7" s="17"/>
+      <x:c r="Q7" s="17"/>
+      <x:c r="R7" s="18"/>
+      <x:c r="S7" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T7" s="3" t="str">
+      <x:c r="T7" s="10" t="str">
         <x:v>Delta</x:v>
       </x:c>
-      <x:c r="U7" s="3" t="str">
+      <x:c r="U7" s="10" t="str">
         <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
       </x:c>
-      <x:c r="V7" s="3" t="e">
+      <x:c r="V7" s="10" t="e">
         <x:f>HYPERLINK("https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html","https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html, friendlyName=https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="43.20000076293945" hidden="0" customHeight="1">
-      <x:c r="A8" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B8" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="str">
+      <x:c r="A8" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
         <x:v>2026-10-17:14</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="str">
+      <x:c r="D8" s="10" t="str">
         <x:v>台灣</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="str">
+      <x:c r="E8" s="10" t="str">
         <x:v>玻璃基板；光通訊；先進封裝</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="str">
+      <x:c r="F8" s="10" t="str">
         <x:v>純面板營收占比目標</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="str">
+      <x:c r="G8" s="10" t="str">
         <x:v>公司目標</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="str">
+      <x:c r="H8" s="10" t="str">
         <x:v>2030</x:v>
       </x:c>
-      <x:c r="I8" s="11" t="n">
+      <x:c r="I8" s="19" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="str">
+      <x:c r="J8" s="10" t="str">
         <x:v>%</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="str"/>
-      <x:c r="L8" s="11"/>
-      <x:c r="M8" s="3" t="str">
+      <x:c r="K8" s="10" t="str"/>
+      <x:c r="L8" s="19"/>
+      <x:c r="M8" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N8" s="10"/>
-      <x:c r="O8" s="10"/>
-      <x:c r="P8" s="9"/>
-      <x:c r="Q8" s="9"/>
-      <x:c r="R8" s="10"/>
-      <x:c r="S8" s="3" t="str">
+      <x:c r="N8" s="18"/>
+      <x:c r="O8" s="18"/>
+      <x:c r="P8" s="17"/>
+      <x:c r="Q8" s="17"/>
+      <x:c r="R8" s="18"/>
+      <x:c r="S8" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T8" s="3" t="str">
+      <x:c r="T8" s="10" t="str">
         <x:v>AUO 董事長，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U8" s="3" t="str">
+      <x:c r="U8" s="10" t="str">
         <x:v>分析：先辨識新材料製程使用哪些設備、是否增加電源控制要求，再決定工程投入。零組件轉型可能形成設備需求，現階段未有可量化的 AEIS 訂單或資本支出影響。</x:v>
       </x:c>
-      <x:c r="V8" s="3" t="e">
+      <x:c r="V8" s="10" t="e">
         <x:f>HYPERLINK("https://www.cna.com.tw/news/afe/202610170118.aspx","https://www.cna.com.tw/news/afe/202610170118.aspx")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://www.cna.com.tw/news/afe/202610170118.aspx, friendlyName=https://www.cna.com.tw/news/afe/202610170118.aspx</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="72" hidden="0" customHeight="1">
-      <x:c r="A9" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B9" s="8" t="d">
+      <x:c r="A9" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>2026-10-17:15</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="str">
+      <x:c r="D9" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E9" s="3" t="str">
+      <x:c r="E9" s="10" t="str">
         <x:v>終端 AI；PC；IC 設計；封裝</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="str">
+      <x:c r="F9" s="10" t="str">
         <x:v>最高統一記憶體規格</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="str">
+      <x:c r="G9" s="10" t="str">
         <x:v>產品規格</x:v>
       </x:c>
-      <x:c r="H9" s="3" t="str">
+      <x:c r="H9" s="10" t="str">
         <x:v>2026-10-16 發布</x:v>
       </x:c>
-      <x:c r="I9" s="9" t="n">
+      <x:c r="I9" s="17" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="J9" s="3" t="str">
+      <x:c r="J9" s="10" t="str">
         <x:v>GB</x:v>
       </x:c>
-      <x:c r="K9" s="3" t="str"/>
-      <x:c r="L9" s="9"/>
-      <x:c r="M9" s="3" t="str">
+      <x:c r="K9" s="10" t="str"/>
+      <x:c r="L9" s="17"/>
+      <x:c r="M9" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N9" s="10"/>
-      <x:c r="O9" s="10"/>
-      <x:c r="P9" s="9"/>
-      <x:c r="Q9" s="9"/>
-      <x:c r="R9" s="10"/>
-      <x:c r="S9" s="3" t="str">
+      <x:c r="N9" s="18"/>
+      <x:c r="O9" s="18"/>
+      <x:c r="P9" s="17"/>
+      <x:c r="Q9" s="17"/>
+      <x:c r="R9" s="18"/>
+      <x:c r="S9" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T9" s="3" t="str">
+      <x:c r="T9" s="10" t="str">
         <x:v>NVIDIA</x:v>
       </x:c>
-      <x:c r="U9" s="3" t="str">
+      <x:c r="U9" s="10" t="str">
         <x:v>分析：分別追蹤前段設備電源、封裝設備及 PC 系統電源的可服務範圍。新品上市尚不足以調高供應量，應等待通路售出、企業導入、退貨率與平台毛利。</x:v>
       </x:c>
-      <x:c r="V9" s="3" t="e">
+      <x:c r="V9" s="10" t="e">
         <x:f>HYPERLINK("https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs","https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs, friendlyName=https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="43.20000076293945" hidden="0" customHeight="1">
-      <x:c r="A10" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B10" s="8" t="d">
+      <x:c r="A10" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C10" s="3" t="str">
+      <x:c r="C10" s="10" t="str">
         <x:v>2026-10-17:4</x:v>
       </x:c>
-      <x:c r="D10" s="3" t="str">
+      <x:c r="D10" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E10" s="3" t="str">
+      <x:c r="E10" s="10" t="str">
         <x:v>海外工業園區；電子供應鏈</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="str">
+      <x:c r="F10" s="10" t="str">
         <x:v>每座園區估算下限</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="str">
+      <x:c r="G10" s="10" t="str">
         <x:v>規劃估算</x:v>
       </x:c>
-      <x:c r="H10" s="3" t="str">
+      <x:c r="H10" s="10" t="str">
         <x:v>規劃期未定</x:v>
       </x:c>
-      <x:c r="I10" s="9" t="n">
+      <x:c r="I10" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J10" s="3" t="str">
+      <x:c r="J10" s="10" t="str">
         <x:v>USD billion</x:v>
       </x:c>
-      <x:c r="K10" s="3" t="str"/>
-      <x:c r="L10" s="9"/>
-      <x:c r="M10" s="3" t="str">
+      <x:c r="K10" s="10" t="str"/>
+      <x:c r="L10" s="17"/>
+      <x:c r="M10" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N10" s="10"/>
-      <x:c r="O10" s="10"/>
-      <x:c r="P10" s="9"/>
-      <x:c r="Q10" s="9"/>
-      <x:c r="R10" s="10"/>
-      <x:c r="S10" s="3" t="str">
+      <x:c r="N10" s="18"/>
+      <x:c r="O10" s="18"/>
+      <x:c r="P10" s="17"/>
+      <x:c r="Q10" s="17"/>
+      <x:c r="R10" s="18"/>
+      <x:c r="S10" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T10" s="3" t="str">
+      <x:c r="T10" s="10" t="str">
         <x:v>經濟部，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U10" s="3" t="str">
+      <x:c r="U10" s="10" t="str">
         <x:v>大型客戶在美國蓋廠，只完成供應鏈在地化的一部分。對中小供應商，關鍵是園區能否提供穩定訂單、共用設施與可負擔的資金，而不只是一塊海外土地。</x:v>
       </x:c>
-      <x:c r="V10" s="3" t="e">
+      <x:c r="V10" s="10" t="e">
         <x:f>HYPERLINK("https://www.cna.com.tw/news/afe/202610160128.aspx","https://www.cna.com.tw/news/afe/202610160128.aspx")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://www.cna.com.tw/news/afe/202610160128.aspx, friendlyName=https://www.cna.com.tw/news/afe/202610160128.aspx</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="43.20000076293945" hidden="0" customHeight="1">
-      <x:c r="A11" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B11" s="8" t="d">
+      <x:c r="A11" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C11" s="3" t="str">
+      <x:c r="C11" s="10" t="str">
         <x:v>2026-10-17:4</x:v>
       </x:c>
-      <x:c r="D11" s="3" t="str">
+      <x:c r="D11" s="10" t="str">
         <x:v>台灣；美國</x:v>
       </x:c>
-      <x:c r="E11" s="3" t="str">
+      <x:c r="E11" s="10" t="str">
         <x:v>海外工業園區；電子供應鏈</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="str">
+      <x:c r="F11" s="10" t="str">
         <x:v>每座園區估算上限</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="str">
+      <x:c r="G11" s="10" t="str">
         <x:v>規劃估算</x:v>
       </x:c>
-      <x:c r="H11" s="3" t="str">
+      <x:c r="H11" s="10" t="str">
         <x:v>規劃期未定</x:v>
       </x:c>
-      <x:c r="I11" s="9" t="n">
+      <x:c r="I11" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J11" s="3" t="str">
+      <x:c r="J11" s="10" t="str">
         <x:v>USD billion</x:v>
       </x:c>
-      <x:c r="K11" s="3" t="str"/>
-      <x:c r="L11" s="9"/>
-      <x:c r="M11" s="3" t="str">
+      <x:c r="K11" s="10" t="str"/>
+      <x:c r="L11" s="17"/>
+      <x:c r="M11" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N11" s="10"/>
-      <x:c r="O11" s="10"/>
-      <x:c r="P11" s="9"/>
-      <x:c r="Q11" s="9"/>
-      <x:c r="R11" s="10"/>
-      <x:c r="S11" s="3" t="str">
+      <x:c r="N11" s="18"/>
+      <x:c r="O11" s="18"/>
+      <x:c r="P11" s="17"/>
+      <x:c r="Q11" s="17"/>
+      <x:c r="R11" s="18"/>
+      <x:c r="S11" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T11" s="3" t="str">
+      <x:c r="T11" s="10" t="str">
         <x:v>經濟部，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U11" s="3" t="str">
+      <x:c r="U11" s="10" t="str">
         <x:v>大型客戶在美國蓋廠，只完成供應鏈在地化的一部分。對中小供應商，關鍵是園區能否提供穩定訂單、共用設施與可負擔的資金，而不只是一塊海外土地。</x:v>
       </x:c>
-      <x:c r="V11" s="3" t="e">
+      <x:c r="V11" s="10" t="e">
         <x:f>HYPERLINK("https://www.cna.com.tw/news/afe/202610160128.aspx","https://www.cna.com.tw/news/afe/202610160128.aspx")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://www.cna.com.tw/news/afe/202610160128.aspx, friendlyName=https://www.cna.com.tw/news/afe/202610160128.aspx</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="72" hidden="0" customHeight="1">
-      <x:c r="A12" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B12" s="8" t="d">
+      <x:c r="A12" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C12" s="3" t="str">
+      <x:c r="C12" s="10" t="str">
         <x:v>2026-10-17:11</x:v>
       </x:c>
-      <x:c r="D12" s="3" t="str">
+      <x:c r="D12" s="10" t="str">
         <x:v>台灣</x:v>
       </x:c>
-      <x:c r="E12" s="3" t="str">
+      <x:c r="E12" s="10" t="str">
         <x:v>總體經濟；AI 投資</x:v>
       </x:c>
-      <x:c r="F12" s="3" t="str">
+      <x:c r="F12" s="10" t="str">
         <x:v>2026 年 GDP 成長預測</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="str">
+      <x:c r="G12" s="10" t="str">
         <x:v>預測</x:v>
       </x:c>
-      <x:c r="H12" s="3" t="str">
+      <x:c r="H12" s="10" t="str">
         <x:v>2026 全年，2026-10 預測版</x:v>
       </x:c>
-      <x:c r="I12" s="11" t="n">
+      <x:c r="I12" s="19" t="n">
         <x:v>0.1216</x:v>
       </x:c>
-      <x:c r="J12" s="3" t="str">
+      <x:c r="J12" s="10" t="str">
         <x:v>%</x:v>
       </x:c>
-      <x:c r="K12" s="3" t="str">
+      <x:c r="K12" s="10" t="str">
         <x:v>2026 全年，2026-07 預測版</x:v>
       </x:c>
-      <x:c r="L12" s="11" t="n">
+      <x:c r="L12" s="19" t="n">
         <x:v>0.1035</x:v>
       </x:c>
-      <x:c r="M12" s="3" t="str">
+      <x:c r="M12" s="10" t="str">
         <x:v>預測修訂</x:v>
       </x:c>
-      <x:c r="N12" s="10"/>
-      <x:c r="O12" s="10"/>
-      <x:c r="P12" s="9"/>
-      <x:c r="Q12" s="9" t="n">
+      <x:c r="N12" s="18"/>
+      <x:c r="O12" s="18"/>
+      <x:c r="P12" s="17"/>
+      <x:c r="Q12" s="17" t="n">
         <x:f>(I12-L12)*100</x:f>
         <x:v>1.8100000000000005</x:v>
       </x:c>
-      <x:c r="R12" s="10"/>
-      <x:c r="S12" s="3" t="str">
+      <x:c r="R12" s="18"/>
+      <x:c r="S12" s="10" t="str">
         <x:v>已揭露</x:v>
       </x:c>
-      <x:c r="T12" s="3" t="str">
+      <x:c r="T12" s="10" t="str">
         <x:v>CIER</x:v>
       </x:c>
-      <x:c r="U12" s="3" t="str">
+      <x:c r="U12" s="10" t="str">
         <x:v>這份預測的重點是 AI 硬體需求如何傳到投資與消費。分析時仍要分清：少數出口產業的強勁成長、整體 GDP，以及每個人的收入感受，三者不會等比例變動。</x:v>
       </x:c>
-      <x:c r="V12" s="3" t="e">
+      <x:c r="V12" s="10" t="e">
         <x:f>HYPERLINK("https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/","https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/, friendlyName=https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="72" hidden="0" customHeight="1">
-      <x:c r="A13" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B13" s="8" t="d">
+      <x:c r="A13" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C13" s="3" t="str">
+      <x:c r="C13" s="10" t="str">
         <x:v>2026-10-17:18</x:v>
       </x:c>
-      <x:c r="D13" s="3" t="str">
+      <x:c r="D13" s="10" t="str">
         <x:v>越南</x:v>
       </x:c>
-      <x:c r="E13" s="3" t="str">
+      <x:c r="E13" s="10" t="str">
         <x:v>AI 資料中心；電源；能源</x:v>
       </x:c>
-      <x:c r="F13" s="3" t="str">
+      <x:c r="F13" s="10" t="str">
         <x:v>既有資料中心投資計畫</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="str">
+      <x:c r="G13" s="10" t="str">
         <x:v>既有規劃</x:v>
       </x:c>
-      <x:c r="H13" s="3" t="str">
+      <x:c r="H13" s="10" t="str">
         <x:v>2026-03 公布，2026-10 電價追蹤</x:v>
       </x:c>
-      <x:c r="I13" s="9" t="n">
+      <x:c r="I13" s="17" t="n">
         <x:v>2.1</x:v>
       </x:c>
-      <x:c r="J13" s="3" t="str">
+      <x:c r="J13" s="10" t="str">
         <x:v>USD billion</x:v>
       </x:c>
-      <x:c r="K13" s="3" t="str"/>
-      <x:c r="L13" s="9"/>
-      <x:c r="M13" s="3" t="str">
+      <x:c r="K13" s="10" t="str"/>
+      <x:c r="L13" s="17"/>
+      <x:c r="M13" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N13" s="10"/>
-      <x:c r="O13" s="10"/>
-      <x:c r="P13" s="9"/>
-      <x:c r="Q13" s="9"/>
-      <x:c r="R13" s="10"/>
-      <x:c r="S13" s="3" t="str">
+      <x:c r="N13" s="18"/>
+      <x:c r="O13" s="18"/>
+      <x:c r="P13" s="17"/>
+      <x:c r="Q13" s="17"/>
+      <x:c r="R13" s="18"/>
+      <x:c r="S13" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T13" s="3" t="str">
+      <x:c r="T13" s="10" t="str">
         <x:v>AIC / KBC，由 TNGlobal 報導</x:v>
       </x:c>
-      <x:c r="U13" s="3" t="str">
+      <x:c r="U13" s="10" t="str">
         <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 AEIS 收入或投資回收。</x:v>
       </x:c>
-      <x:c r="V13" s="3" t="e">
+      <x:c r="V13" s="10" t="e">
         <x:f>HYPERLINK("https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/","https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/, friendlyName=https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="72" hidden="0" customHeight="1">
-      <x:c r="A14" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B14" s="8" t="d">
+      <x:c r="A14" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C14" s="3" t="str">
+      <x:c r="C14" s="10" t="str">
         <x:v>2026-10-17:19</x:v>
       </x:c>
-      <x:c r="D14" s="3" t="str">
+      <x:c r="D14" s="10" t="str">
         <x:v>馬來西亞；台灣</x:v>
       </x:c>
-      <x:c r="E14" s="3" t="str">
+      <x:c r="E14" s="10" t="str">
         <x:v>半導體；後段封測；設備服務</x:v>
       </x:c>
-      <x:c r="F14" s="3" t="str">
+      <x:c r="F14" s="10" t="str">
         <x:v>活動職缺下限</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="str">
+      <x:c r="G14" s="10" t="str">
         <x:v>超過此數，非實際聘用</x:v>
       </x:c>
-      <x:c r="H14" s="3" t="str">
+      <x:c r="H14" s="10" t="str">
         <x:v>2026-10-14 至 2026-10-17</x:v>
       </x:c>
-      <x:c r="I14" s="9" t="n">
+      <x:c r="I14" s="17" t="n">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="J14" s="3" t="str">
+      <x:c r="J14" s="10" t="str">
         <x:v>個職缺</x:v>
       </x:c>
-      <x:c r="K14" s="3" t="str"/>
-      <x:c r="L14" s="9"/>
-      <x:c r="M14" s="3" t="str">
+      <x:c r="K14" s="10" t="str"/>
+      <x:c r="L14" s="17"/>
+      <x:c r="M14" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N14" s="10"/>
-      <x:c r="O14" s="10"/>
-      <x:c r="P14" s="9"/>
-      <x:c r="Q14" s="9"/>
-      <x:c r="R14" s="10"/>
-      <x:c r="S14" s="3" t="str">
+      <x:c r="N14" s="18"/>
+      <x:c r="O14" s="18"/>
+      <x:c r="P14" s="17"/>
+      <x:c r="Q14" s="17"/>
+      <x:c r="R14" s="18"/>
+      <x:c r="S14" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T14" s="3" t="str">
+      <x:c r="T14" s="10" t="str">
         <x:v>主辦活動，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U14" s="3" t="str">
+      <x:c r="U14" s="10" t="str">
         <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 AEIS 合作、客戶採購或新的工廠投資。</x:v>
       </x:c>
-      <x:c r="V14" s="3" t="e">
+      <x:c r="V14" s="10" t="e">
         <x:f>HYPERLINK("https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side","https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side, friendlyName=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="72" hidden="0" customHeight="1">
-      <x:c r="A15" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B15" s="8" t="d">
+      <x:c r="A15" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C15" s="3" t="str">
+      <x:c r="C15" s="10" t="str">
         <x:v>2026-10-17:19</x:v>
       </x:c>
-      <x:c r="D15" s="3" t="str">
+      <x:c r="D15" s="10" t="str">
         <x:v>馬來西亞；台灣</x:v>
       </x:c>
-      <x:c r="E15" s="3" t="str">
+      <x:c r="E15" s="10" t="str">
         <x:v>半導體；後段封測；設備服務</x:v>
       </x:c>
-      <x:c r="F15" s="3" t="str">
+      <x:c r="F15" s="10" t="str">
         <x:v>園區公司數</x:v>
       </x:c>
-      <x:c r="G15" s="3" t="str">
+      <x:c r="G15" s="10" t="str">
         <x:v>官方陳述</x:v>
       </x:c>
-      <x:c r="H15" s="3" t="str">
+      <x:c r="H15" s="10" t="str">
         <x:v>2026-10-16 官員說明</x:v>
       </x:c>
-      <x:c r="I15" s="9" t="n">
+      <x:c r="I15" s="17" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J15" s="3" t="str">
+      <x:c r="J15" s="10" t="str">
         <x:v>家</x:v>
       </x:c>
-      <x:c r="K15" s="3" t="str"/>
-      <x:c r="L15" s="9"/>
-      <x:c r="M15" s="3" t="str">
+      <x:c r="K15" s="10" t="str"/>
+      <x:c r="L15" s="17"/>
+      <x:c r="M15" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N15" s="10"/>
-      <x:c r="O15" s="10"/>
-      <x:c r="P15" s="9"/>
-      <x:c r="Q15" s="9"/>
-      <x:c r="R15" s="10"/>
-      <x:c r="S15" s="3" t="str">
+      <x:c r="N15" s="18"/>
+      <x:c r="O15" s="18"/>
+      <x:c r="P15" s="17"/>
+      <x:c r="Q15" s="17"/>
+      <x:c r="R15" s="18"/>
+      <x:c r="S15" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T15" s="3" t="str">
+      <x:c r="T15" s="10" t="str">
         <x:v>雪蘭莪官員，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U15" s="3" t="str">
+      <x:c r="U15" s="10" t="str">
         <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 AEIS 合作、客戶採購或新的工廠投資。</x:v>
       </x:c>
-      <x:c r="V15" s="3" t="e">
+      <x:c r="V15" s="10" t="e">
         <x:f>HYPERLINK("https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side","https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side, friendlyName=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="72" hidden="0" customHeight="1">
-      <x:c r="A16" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B16" s="8" t="d">
+      <x:c r="A16" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="d">
         <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C16" s="3" t="str">
+      <x:c r="C16" s="10" t="str">
         <x:v>2026-10-17:19</x:v>
       </x:c>
-      <x:c r="D16" s="3" t="str">
+      <x:c r="D16" s="10" t="str">
         <x:v>馬來西亞；台灣</x:v>
       </x:c>
-      <x:c r="E16" s="3" t="str">
+      <x:c r="E16" s="10" t="str">
         <x:v>半導體；後段封測；設備服務</x:v>
       </x:c>
-      <x:c r="F16" s="3" t="str">
+      <x:c r="F16" s="10" t="str">
         <x:v>園區工程師數</x:v>
       </x:c>
-      <x:c r="G16" s="3" t="str">
+      <x:c r="G16" s="10" t="str">
         <x:v>官方陳述</x:v>
       </x:c>
-      <x:c r="H16" s="3" t="str">
+      <x:c r="H16" s="10" t="str">
         <x:v>2026-10-16 官員說明</x:v>
       </x:c>
-      <x:c r="I16" s="9" t="n">
+      <x:c r="I16" s="17" t="n">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="J16" s="3" t="str">
+      <x:c r="J16" s="10" t="str">
         <x:v>人</x:v>
       </x:c>
-      <x:c r="K16" s="3" t="str"/>
-      <x:c r="L16" s="9"/>
-      <x:c r="M16" s="3" t="str">
+      <x:c r="K16" s="10" t="str"/>
+      <x:c r="L16" s="17"/>
+      <x:c r="M16" s="10" t="str">
         <x:v>無</x:v>
       </x:c>
-      <x:c r="N16" s="10"/>
-      <x:c r="O16" s="10"/>
-      <x:c r="P16" s="9"/>
-      <x:c r="Q16" s="9"/>
-      <x:c r="R16" s="10"/>
-      <x:c r="S16" s="3" t="str">
+      <x:c r="N16" s="18"/>
+      <x:c r="O16" s="18"/>
+      <x:c r="P16" s="17"/>
+      <x:c r="Q16" s="17"/>
+      <x:c r="R16" s="18"/>
+      <x:c r="S16" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T16" s="3" t="str">
+      <x:c r="T16" s="10" t="str">
         <x:v>雪蘭莪官員，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U16" s="3" t="str">
+      <x:c r="U16" s="10" t="str">
         <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 AEIS 合作、客戶採購或新的工廠投資。</x:v>
       </x:c>
-      <x:c r="V16" s="3" t="e">
+      <x:c r="V16" s="10" t="e">
         <x:f>HYPERLINK("https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side","https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side, friendlyName=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="72" hidden="0" customHeight="1">
-      <x:c r="A17" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B17" s="8" t="d">
+      <x:c r="A17" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C17" s="3" t="str">
+      <x:c r="C17" s="10" t="str">
         <x:v>2026-10-17:20</x:v>
       </x:c>
-      <x:c r="D17" s="3" t="str">
+      <x:c r="D17" s="10" t="str">
         <x:v>越南；新加坡</x:v>
       </x:c>
-      <x:c r="E17" s="3" t="str">
+      <x:c r="E17" s="10" t="str">
         <x:v>製造業；外商投資；工業電源</x:v>
       </x:c>
-      <x:c r="F17" s="3" t="str">
+      <x:c r="F17" s="10" t="str">
         <x:v>FDI 實現額估計</x:v>
       </x:c>
-      <x:c r="G17" s="3" t="str">
+      <x:c r="G17" s="10" t="str">
         <x:v>官方估計</x:v>
       </x:c>
-      <x:c r="H17" s="3" t="str">
+      <x:c r="H17" s="10" t="str">
         <x:v>2026-01 至 2026-09</x:v>
       </x:c>
-      <x:c r="I17" s="9" t="n">
+      <x:c r="I17" s="17" t="n">
         <x:v>21.07</x:v>
       </x:c>
-      <x:c r="J17" s="3" t="str">
+      <x:c r="J17" s="10" t="str">
         <x:v>USD billion</x:v>
       </x:c>
-      <x:c r="K17" s="3" t="str">
+      <x:c r="K17" s="10" t="str">
         <x:v>2025-01 至 2025-09</x:v>
       </x:c>
-      <x:c r="L17" s="9"/>
-      <x:c r="M17" s="3" t="str">
+      <x:c r="L17" s="17"/>
+      <x:c r="M17" s="10" t="str">
         <x:v>YoY</x:v>
       </x:c>
-      <x:c r="N17" s="10" t="n">
+      <x:c r="N17" s="18" t="n">
         <x:v>0.121</x:v>
       </x:c>
-      <x:c r="O17" s="10"/>
-      <x:c r="P17" s="9"/>
-      <x:c r="Q17" s="9"/>
-      <x:c r="R17" s="10"/>
-      <x:c r="S17" s="3" t="str">
+      <x:c r="O17" s="18"/>
+      <x:c r="P17" s="17"/>
+      <x:c r="Q17" s="17"/>
+      <x:c r="R17" s="18"/>
+      <x:c r="S17" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T17" s="3" t="str">
+      <x:c r="T17" s="10" t="str">
         <x:v>越南國家統計局，由政府新聞網公布</x:v>
       </x:c>
-      <x:c r="U17" s="3" t="str">
+      <x:c r="U17" s="10" t="str">
         <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 AEIS 的成長率。</x:v>
       </x:c>
-      <x:c r="V17" s="3" t="e">
+      <x:c r="V17" s="10" t="e">
         <x:f>HYPERLINK("https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm","https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm, friendlyName=https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="72" hidden="0" customHeight="1">
-      <x:c r="A18" s="8" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B18" s="8" t="d">
+      <x:c r="A18" s="14" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C18" s="3" t="str">
+      <x:c r="C18" s="11" t="str">
         <x:v>2026-10-17:20</x:v>
       </x:c>
-      <x:c r="D18" s="3" t="str">
+      <x:c r="D18" s="11" t="str">
         <x:v>越南；新加坡</x:v>
       </x:c>
-      <x:c r="E18" s="3" t="str">
+      <x:c r="E18" s="11" t="str">
         <x:v>製造業；外商投資；工業電源</x:v>
       </x:c>
-      <x:c r="F18" s="3" t="str">
+      <x:c r="F18" s="11" t="str">
         <x:v>總註冊外資</x:v>
       </x:c>
-      <x:c r="G18" s="3" t="str">
+      <x:c r="G18" s="11" t="str">
         <x:v>官方統計</x:v>
       </x:c>
-      <x:c r="H18" s="3" t="str">
+      <x:c r="H18" s="11" t="str">
         <x:v>2026-01 至 2026-09</x:v>
       </x:c>
-      <x:c r="I18" s="9" t="n">
+      <x:c r="I18" s="20" t="n">
         <x:v>50.36</x:v>
       </x:c>
-      <x:c r="J18" s="3" t="str">
+      <x:c r="J18" s="11" t="str">
         <x:v>USD billion</x:v>
       </x:c>
-      <x:c r="K18" s="3" t="str">
+      <x:c r="K18" s="11" t="str">
         <x:v>2025-01 至 2025-09</x:v>
       </x:c>
-      <x:c r="L18" s="9"/>
-      <x:c r="M18" s="3" t="str">
+      <x:c r="L18" s="20"/>
+      <x:c r="M18" s="11" t="str">
         <x:v>YoY</x:v>
       </x:c>
-      <x:c r="N18" s="10" t="n">
+      <x:c r="N18" s="21" t="n">
         <x:v>0.764</x:v>
       </x:c>
-      <x:c r="O18" s="10"/>
-      <x:c r="P18" s="9"/>
-      <x:c r="Q18" s="9"/>
-      <x:c r="R18" s="10"/>
-      <x:c r="S18" s="3" t="str">
+      <x:c r="O18" s="21"/>
+      <x:c r="P18" s="20"/>
+      <x:c r="Q18" s="20"/>
+      <x:c r="R18" s="21"/>
+      <x:c r="S18" s="11" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T18" s="3" t="str">
+      <x:c r="T18" s="11" t="str">
         <x:v>越南國家統計局，由政府新聞網公布</x:v>
       </x:c>
-      <x:c r="U18" s="3" t="str">
+      <x:c r="U18" s="11" t="str">
         <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 AEIS 的成長率。</x:v>
       </x:c>
-      <x:c r="V18" s="3" t="e">
+      <x:c r="V18" s="11" t="e">
         <x:f>HYPERLINK("https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm","https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm, friendlyName=https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm</x:v>
       </x:c>
@@ -2059,7 +2123,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4c711fdf80447a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c62177345ab4e9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2084,129 +2148,129 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="3" t="str">
+      <x:c r="A2" s="9" t="str">
         <x:v>閱讀角度</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="9" t="str">
         <x:v>Advanced Energy Industries (NASDAQ: AEIS)。半導體設備精密電源、資料中心電源、工業客戶與區域服務；影響為編輯分析。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="3" t="str">
+      <x:c r="A3" s="10" t="str">
         <x:v>國家範圍</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>聚焦台灣與東南亞。美國等國家只在直接連結台灣供應鏈時列為關聯地點。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="3" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>日期</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>刊期與事件日期分欄。週報刊期欄為週起日，個別事件日期請查數值明細與日報。背景資料保留原發布時間。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A5" s="3" t="str">
+      <x:c r="A5" s="10" t="str">
         <x:v>市場動向</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>日報每則一列。週報依精選五個主題合併，數值明細保留各事件。市場表連結至日報完整來源，數值表連結至原始數據。下載完整刊期，不受頁面搜尋篩選影響。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="3" t="str">
+      <x:c r="A6" s="10" t="str">
         <x:v>數值與單位</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="str">
+      <x:c r="B6" s="10" t="str">
         <x:v>數值為可計算儲存格，貨幣單位獨立。百分比底層為小數，顯示百分比。不同公司、期間、產品規格及計畫金額不可任意加總。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="3" t="str">
+      <x:c r="A7" s="10" t="str">
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="B7" s="3" t="str">
+      <x:c r="B7" s="10" t="str">
         <x:v>只填來源明示的同口徑基期。缺少則留空並註明，不從已四捨五入成長率反推精確基期。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="3" t="str">
+      <x:c r="A8" s="10" t="str">
         <x:v>YoY / QoQ</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="str">
+      <x:c r="B8" s="10" t="str">
         <x:v>分欄記錄來源公布的年增率與季增率。數值明細可能用不同列表示同一指標的不同比較口徑。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="3" t="str">
+      <x:c r="A9" s="10" t="str">
         <x:v>變動計算</x:v>
       </x:c>
-      <x:c r="B9" s="3" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>同口徑且基期可用時，金額變動＝本期減基期；變動率＝本期除基期減一。基期為零時變動率留空。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="3" t="str">
+      <x:c r="A10" s="10" t="str">
         <x:v>百分點</x:v>
       </x:c>
-      <x:c r="B10" s="3" t="str">
+      <x:c r="B10" s="10" t="str">
         <x:v>比例或成長率的修訂以百分點表示。例如 GDP 預測由 10.35% 到 12.16%，增加 1.81 個百分點，並非年增 1.81%。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="3" t="str">
+      <x:c r="A11" s="10" t="str">
         <x:v>資料性質</x:v>
       </x:c>
-      <x:c r="B11" s="3" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>區分實績、官方估計、預測、公司目標、規劃與產品規格。規劃不是已實現 FDI，額定能力不是實際用電，職缺不是聘用。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="3" t="str">
+      <x:c r="A12" s="10" t="str">
         <x:v>AEIS 影響</x:v>
       </x:c>
-      <x:c r="B12" s="3" t="str">
+      <x:c r="B12" s="10" t="str">
         <x:v>來源沒有披露 AEIS 訂單或影響金額時保持未知，不以市場增幅直接推算公司收入。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="3" t="str">
+      <x:c r="A13" s="10" t="str">
         <x:v>背景資料</x:v>
       </x:c>
-      <x:c r="B13" s="3" t="str">
+      <x:c r="B13" s="10" t="str">
         <x:v>CoWoS 與美光屬本週追蹤；越南 FDI 於 10/3 發布，非今日新統計。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="57.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A14" s="3" t="str">
+      <x:c r="A14" s="10" t="str">
         <x:v>來源限制</x:v>
       </x:c>
-      <x:c r="B14" s="3" t="str">
+      <x:c r="B14" s="10" t="str">
         <x:v>本期聚焦台灣與東南亞，更新至台北時間 10 月 17 日晚間。CoWoS、美光及越南 10 月 3 日 FDI 資料明列為本週追蹤或區域背景。展示規格、友達目標、園區估算與 GDP 預測均非實際訂單。友達及馬來西亞園區數字依具名採訪；胡志明市電價依專業報導，未取得原始會議文件或最終費率，屬來源受限。AEIS 影響評估為編輯分析，未披露的訂單與金額保持未知。Excel 缺少基期時保留空白及原因，YoY 與百分點分開。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="28.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A15" s="3" t="str">
+      <x:c r="A15" s="10" t="str">
         <x:v>AEIS 業務背景</x:v>
       </x:c>
-      <x:c r="B15" s="3" t="str">
+      <x:c r="B15" s="10" t="str">
         <x:v>https://ir.advancedenergy.com/media/document/fcbde7e4-483b-4dcc-93cc-985a436746b5/assets/2026-09_AEIS_IR_Presentation.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="3" t="str">
+      <x:c r="A16" s="11" t="str">
         <x:v>資料更新</x:v>
       </x:c>
-      <x:c r="B16" s="3" t="d">
+      <x:c r="B16" s="11" t="d">
         <x:v>2026-10-17T10:45:57.185Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R459fdd0865084568"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb93ff0d991ad4052"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="市場動向" sheetId="1" r:id="R6b94f833ed9049e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="數值明細" sheetId="2" r:id="Ra0658e161b7e4912"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位說明" sheetId="3" r:id="Rd6776d5bdc7b4b11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="市場動向" sheetId="1" r:id="Ree6ca0fc10854099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="數值明細" sheetId="2" r:id="Rd15165484d5f4a9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位說明" sheetId="3" r:id="R422d59829d4044f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -168,9 +168,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MarketEvents" displayName="MarketEvents" ref="A1:S10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:S10"/>
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MarketEvents" displayName="MarketEvents" ref="A1:T11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:T11"/>
+  <x:tableColumns count="20">
     <x:tableColumn id="1" name="刊期日期"/>
     <x:tableColumn id="2" name="事件日期"/>
     <x:tableColumn id="3" name="新聞 ID"/>
@@ -182,22 +182,23 @@
     <x:tableColumn id="9" name="外商投資 FDI"/>
     <x:tableColumn id="10" name="標題"/>
     <x:tableColumn id="11" name="事件摘要"/>
-    <x:tableColumn id="12" name="AEIS 業務關聯"/>
+    <x:tableColumn id="12" name="業務關聯"/>
     <x:tableColumn id="13" name="影響評估（分析）"/>
     <x:tableColumn id="14" name="影響時程"/>
     <x:tableColumn id="15" name="建議檢查事項"/>
     <x:tableColumn id="16" name="下一驗證點"/>
     <x:tableColumn id="17" name="查證信心"/>
     <x:tableColumn id="18" name="來源類型"/>
-    <x:tableColumn id="19" name="來源連結"/>
+    <x:tableColumn id="19" name="完整來源與日報連結"/>
+    <x:tableColumn id="20" name="活動或專案地點"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="QuantitativeDetails" displayName="QuantitativeDetails" ref="A1:V18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:V18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="QuantitativeDetails" displayName="QuantitativeDetails" ref="A1:V22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:V22"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="刊期日期"/>
     <x:tableColumn id="2" name="事件日期"/>
@@ -219,7 +220,7 @@
     <x:tableColumn id="18" name="計算變動率"/>
     <x:tableColumn id="19" name="基期與計算說明"/>
     <x:tableColumn id="20" name="數字歸屬"/>
-    <x:tableColumn id="21" name="對 AEIS 影響評估（分析）"/>
+    <x:tableColumn id="21" name="營運影響評估（分析）"/>
     <x:tableColumn id="22" name="來源連結"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -453,7 +454,8 @@
     <x:col min="16" max="16" width="48" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="28" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="62" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="62" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -491,7 +493,7 @@
         <x:v>事件摘要</x:v>
       </x:c>
       <x:c r="L1" s="7" t="str">
-        <x:v>AEIS 業務關聯</x:v>
+        <x:v>業務關聯</x:v>
       </x:c>
       <x:c r="M1" s="7" t="str">
         <x:v>影響評估（分析）</x:v>
@@ -514,8 +516,11 @@
       <x:c r="S1" s="7" t="str">
         <x:v>完整來源與日報連結</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="T1" s="7" t="str">
+        <x:v>活動或專案地點</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -553,7 +558,7 @@
         <x:v>半導體設備精密電源，間接需求</x:v>
       </x:c>
       <x:c r="M2" s="9" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
+        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
       </x:c>
       <x:c r="N2" s="9" t="str">
         <x:v>近期認證與中期設備拉貨</x:v>
@@ -568,14 +573,16 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="R2" s="9" t="str">
-        <x:v>First-hand</x:v>
-      </x:c>
-      <x:c r="S2" s="9" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-12","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-12, friendlyName=完整來源與日報</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="86.4000015258789" hidden="0" customHeight="1">
+        <x:v>First-hand; Second-hand</x:v>
+      </x:c>
+      <x:c r="S2" s="9" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-12</x:v>
+      </x:c>
+      <x:c r="T2" s="9" t="str">
+        <x:v>美光啟用典禮：台灣台中，美光先進封裝測試二廠（AATT2）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="57.599998474121094" hidden="0" customHeight="1">
       <x:c r="A3" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -607,10 +614,10 @@
         <x:v>OCP 台廠展示整機櫃、800 VDC 電源與液冷，量產驗收成為下一關</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>中央社 10 月 17 日整理 10 月 12 至 15 日 OCP 展會：緯穎、華碩與勤誠等展示下一代伺服器或機櫃，台達電、光寶與康舒展示高壓直流電源及相關方案。台達電 10 月 15 日公司稿列出 800 VDC 電源櫃、備援與液冷產品，展示規格仍需與量產部署分開。</x:v>
+        <x:v>中央社 10 月 17 日整理 10 月 12 至 15 日於美國加州聖荷西舉辦的 OCP 展會：緯穎、華碩與勤誠等展示下一代伺服器或機櫃，台達電、光寶與康舒展示高壓直流電源及相關方案。台達電 10 月 15 日公司稿列出 800 VDC 電源櫃、備援與液冷產品，展示規格仍需與量產部署分開。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>資料中心電源直接相關，未證實 AEIS 新訂單</x:v>
+        <x:v>資料中心電源直接相關，未證實 電源供應商 新訂單</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
         <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
@@ -630,12 +637,14 @@
       <x:c r="R3" s="10" t="str">
         <x:v>Second-hand; First-hand</x:v>
       </x:c>
-      <x:c r="S3" s="10" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-13","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-13, friendlyName=完整來源與日報</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="S3" s="10" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-13</x:v>
+      </x:c>
+      <x:c r="T3" s="10" t="str">
+        <x:v>美國加州聖荷西，San Jose McEnery Convention Center</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A4" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -673,7 +682,7 @@
         <x:v>新材料設備電源的潛在需求</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>分析：先辨識新材料製程使用哪些設備、是否增加電源控制要求，再決定工程投入。零組件轉型可能形成設備需求，現階段未有可量化的 AEIS 訂單或資本支出影響。</x:v>
+        <x:v>分析：先辨識新材料製程使用哪些設備、是否增加電源控制要求，再決定工程投入。零組件轉型可能形成設備需求，現階段未有可量化的 電源供應商 訂單或資本支出影響。</x:v>
       </x:c>
       <x:c r="N4" s="10" t="str">
         <x:v>光通訊量產展望兩至三年，屬公司估計</x:v>
@@ -690,12 +699,14 @@
       <x:c r="R4" s="10" t="str">
         <x:v>Second-hand</x:v>
       </x:c>
-      <x:c r="S4" s="10" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-14","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-14, friendlyName=完整來源與日報</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="S4" s="10" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-14</x:v>
+      </x:c>
+      <x:c r="T4" s="10" t="str">
+        <x:v>未提供活動場館；詳見原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A5" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -750,12 +761,14 @@
       <x:c r="R5" s="10" t="str">
         <x:v>First-hand; Second-hand</x:v>
       </x:c>
-      <x:c r="S5" s="10" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-15","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-15, friendlyName=完整來源與日報</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="S5" s="10" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-15</x:v>
+      </x:c>
+      <x:c r="T5" s="10" t="str">
+        <x:v>未提供活動場館；詳見原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="57.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -810,12 +823,14 @@
       <x:c r="R6" s="10" t="str">
         <x:v>Second-hand</x:v>
       </x:c>
-      <x:c r="S6" s="10" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-4","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-4, friendlyName=完整來源與日報</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="S6" s="10" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-4</x:v>
+      </x:c>
+      <x:c r="T6" s="10" t="str">
+        <x:v>投資規劃：美國德州；具體園區用地仍待確認</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A7" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -870,12 +885,14 @@
       <x:c r="R7" s="10" t="str">
         <x:v>First-hand; Second-hand</x:v>
       </x:c>
-      <x:c r="S7" s="10" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-11","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-11, friendlyName=完整來源與日報</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="S7" s="10" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-11</x:v>
+      </x:c>
+      <x:c r="T7" s="10" t="str">
+        <x:v>未提供活動場館；詳見原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A8" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -913,7 +930,7 @@
         <x:v>資料中心電源，部署時點風險</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 AEIS 收入或投資回收。</x:v>
+        <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 電源供應商 收入或投資回收。</x:v>
       </x:c>
       <x:c r="N8" s="10" t="str">
         <x:v>待費率分類與電力合約</x:v>
@@ -930,12 +947,14 @@
       <x:c r="R8" s="10" t="str">
         <x:v>Second-hand</x:v>
       </x:c>
-      <x:c r="S8" s="10" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-18","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-18, friendlyName=完整來源與日報</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="S8" s="10" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-18</x:v>
+      </x:c>
+      <x:c r="T8" s="10" t="str">
+        <x:v>越南胡志明市；專案位於新富中工業區（Tan Phu Trung Industrial Park）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="57.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -955,7 +974,7 @@
         <x:v>設計至封測及現場工程</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>人才與園區布局，非已確認新廠投資</x:v>
+        <x:v>官員提及馬幣 1.5 億令吉合作計畫，撥款時程未披露</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
         <x:v>逾 1,500 職缺，非實際聘用</x:v>
@@ -967,13 +986,13 @@
         <x:v>馬來西亞半導體招募涵蓋製程、設備與廠務，人才連結台灣供應鏈</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>中央社 10 月 16 日報導，雪蘭莪 10 月 14 至 17 日半導體招募活動提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備及廠務。官員表示兩座 IC 設計園區有 20 家公司、409 名工程師，並將雪蘭莪設計與檳城製造、組裝測試視為互補。</x:v>
+        <x:v>中央社 10 月 16 日報導，雪蘭莪相關機構在吉隆坡會展中心（KLCC）主辦的半導體招募活動提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備及廠務。官員表示兩座 IC 設計園區有 20 家公司、409 名工程師，與檳城製造、組裝測試形成互補。</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str">
         <x:v>區域服務與工程人才，間接相關</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 AEIS 合作、客戶採購或新的工廠投資。</x:v>
+        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
       </x:c>
       <x:c r="N9" s="10" t="str">
         <x:v>當期招募與後續認證</x:v>
@@ -988,77 +1007,143 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="R9" s="10" t="str">
-        <x:v>Second-hand</x:v>
-      </x:c>
-      <x:c r="S9" s="10" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-19","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-19, friendlyName=完整來源與日報</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A10" s="14" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="d">
+        <x:v>Second-hand; First-hand</x:v>
+      </x:c>
+      <x:c r="S9" s="10" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-19</x:v>
+      </x:c>
+      <x:c r="T9" s="10" t="str">
+        <x:v>馬來西亞吉隆坡，吉隆坡會展中心（KLCC）；由雪蘭莪相關機構主辦</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A10" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="str">
+      <x:c r="C10" s="10" t="str">
         <x:v>2026-10-17:20</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="str">
+      <x:c r="D10" s="10" t="str">
         <x:v>越南；新加坡</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="str">
+      <x:c r="E10" s="10" t="str">
         <x:v>製造業；外商投資；工業電源</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="str">
+      <x:c r="F10" s="10" t="str">
         <x:v>資金註冊至工廠落地</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="str">
+      <x:c r="G10" s="10" t="str">
         <x:v>總註冊外資 503.6 億美元</x:v>
       </x:c>
-      <x:c r="H10" s="11" t="str">
+      <x:c r="H10" s="10" t="str">
         <x:v>工廠設備需求尚須分項驗證</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="str">
+      <x:c r="I10" s="10" t="str">
         <x:v>FDI 實現額估 210.7 億美元，YoY 12.1%</x:v>
       </x:c>
-      <x:c r="J10" s="11" t="str">
+      <x:c r="J10" s="10" t="str">
         <x:v>區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開</x:v>
       </x:c>
-      <x:c r="K10" s="11" t="str">
+      <x:c r="K10" s="10" t="str">
         <x:v>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。</x:v>
       </x:c>
-      <x:c r="L10" s="11" t="str">
+      <x:c r="L10" s="10" t="str">
         <x:v>在地工業電源與服務的背景指標</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="str">
-        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 AEIS 的成長率。</x:v>
-      </x:c>
-      <x:c r="N10" s="11" t="str">
+      <x:c r="M10" s="10" t="str">
+        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
+      </x:c>
+      <x:c r="N10" s="10" t="str">
         <x:v>截至 2026 年 9 月的區域背景</x:v>
       </x:c>
-      <x:c r="O10" s="11" t="str">
+      <x:c r="O10" s="10" t="str">
         <x:v>對到具名廠房與設備採購</x:v>
       </x:c>
-      <x:c r="P10" s="11" t="str">
+      <x:c r="P10" s="10" t="str">
         <x:v>製造業分項、電網接入與驗收</x:v>
       </x:c>
-      <x:c r="Q10" s="11" t="str">
-        <x:v>高</x:v>
-      </x:c>
-      <x:c r="R10" s="11" t="str">
+      <x:c r="Q10" s="10" t="str">
+        <x:v>中：總量有官方來源，新增分項待核對原表</x:v>
+      </x:c>
+      <x:c r="R10" s="10" t="str">
         <x:v>First-hand; Second-hand</x:v>
       </x:c>
-      <x:c r="S10" s="11" t="e">
-        <x:f>HYPERLINK("https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-20","完整來源與日報")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-20, friendlyName=完整來源與日報</x:v>
+      <x:c r="S10" s="10" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-20</x:v>
+      </x:c>
+      <x:c r="T10" s="10" t="str">
+        <x:v>越南全國統計；非單一活動或工廠</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A11" s="14" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="d">
+        <x:v>2026-10-14T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>2026-10-17:21</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>台灣供應鏈關聯；導入場域未完整披露</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>工廠 AI；檢測；測試；工業設備</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>算力與設備至終端工廠使用者</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>合作發布，未揭露本期採購或投資金額</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str">
+        <x:v>試點與導入方向，未核實全廠收益</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>未揭露</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str">
+        <x:v>背景追蹤：工廠 AI 合作延伸到檢測、測試與數位分身，收益仍待驗收</x:v>
+      </x:c>
+      <x:c r="K11" s="11" t="str">
+        <x:v>NVIDIA 10 月 14 日公司稿列出 KLA 檢測、Advantest 測試，以及鴻海、FANUC 等工廠 AI 合作。本期把它作為台灣供應鏈與終端工廠的背景追蹤；各場域地點、全面量產時程與全廠投資報酬未完整公開。</x:v>
+      </x:c>
+      <x:c r="L11" s="11" t="str">
+        <x:v>工業設備、製程控制及售後服務</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="str">
+        <x:v>分析：設備與軟體能否改善單一工序，和整廠能否增加可交付產出，是兩個驗收問題。採購前應建立基期，追到良率、停機、返工及現金回收。</x:v>
+      </x:c>
+      <x:c r="N11" s="11" t="str">
+        <x:v>試點至量產驗收，時程未完整公開</x:v>
+      </x:c>
+      <x:c r="O11" s="11" t="str">
+        <x:v>先建立基期，再看良品成本與現金回收</x:v>
+      </x:c>
+      <x:c r="P11" s="11" t="str">
+        <x:v>具名工廠、同條件數據、驗收與維護成本</x:v>
+      </x:c>
+      <x:c r="Q11" s="11" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="R11" s="11" t="str">
+        <x:v>First-hand</x:v>
+      </x:c>
+      <x:c r="S11" s="11" t="str">
+        <x:v>https://aiwlulu.github.io/daily-brief-site/?view=day&amp;date=2026-10-17#story-2026-10-17-21</x:v>
+      </x:c>
+      <x:c r="T11" s="11" t="str">
+        <x:v>全球合作發布；各工廠實際導入地點未完整披露</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06561fd696054592"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf53f71e68ad1478e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1156,13 +1241,13 @@
         <x:v>數字歸屬</x:v>
       </x:c>
       <x:c r="U1" s="7" t="str">
-        <x:v>對 AEIS 影響評估（分析）</x:v>
+        <x:v>營運影響評估（分析）</x:v>
       </x:c>
       <x:c r="V1" s="7" t="str">
         <x:v>來源連結</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="72" hidden="0" customHeight="1">
+    <x:row r="2" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1214,14 +1299,13 @@
         <x:v>TSMC</x:v>
       </x:c>
       <x:c r="U2" s="9" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
-      </x:c>
-      <x:c r="V2" s="9" t="e">
-        <x:f>HYPERLINK("https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf","https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf, friendlyName=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="72" hidden="0" customHeight="1">
+        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
+      </x:c>
+      <x:c r="V2" s="9" t="str">
+        <x:v>https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A3" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1273,14 +1357,13 @@
         <x:v>TSMC</x:v>
       </x:c>
       <x:c r="U3" s="10" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
-      </x:c>
-      <x:c r="V3" s="10" t="e">
-        <x:f>HYPERLINK("https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf","https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf, friendlyName=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="72" hidden="0" customHeight="1">
+        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
+      </x:c>
+      <x:c r="V3" s="10" t="str">
+        <x:v>https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A4" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1328,14 +1411,13 @@
         <x:v>TSMC</x:v>
       </x:c>
       <x:c r="U4" s="10" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
-      </x:c>
-      <x:c r="V4" s="10" t="e">
-        <x:f>HYPERLINK("https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf","https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf, friendlyName=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="72" hidden="0" customHeight="1">
+        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
+      </x:c>
+      <x:c r="V4" s="10" t="str">
+        <x:v>https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A5" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1383,14 +1465,13 @@
         <x:v>TSMC</x:v>
       </x:c>
       <x:c r="U5" s="10" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 AEIS 獲單或收入增加。</x:v>
-      </x:c>
-      <x:c r="V5" s="10" t="e">
-        <x:f>HYPERLINK("https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf","https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf, friendlyName=https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="100.80000305175781" hidden="0" customHeight="1">
+        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
+      </x:c>
+      <x:c r="V5" s="10" t="str">
+        <x:v>https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A6" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1440,12 +1521,11 @@
       <x:c r="U6" s="10" t="str">
         <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
       </x:c>
-      <x:c r="V6" s="10" t="e">
-        <x:f>HYPERLINK("https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html","https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html, friendlyName=https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="100.80000305175781" hidden="0" customHeight="1">
+      <x:c r="V6" s="10" t="str">
+        <x:v>https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A7" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1495,12 +1575,11 @@
       <x:c r="U7" s="10" t="str">
         <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
       </x:c>
-      <x:c r="V7" s="10" t="e">
-        <x:f>HYPERLINK("https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html","https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html, friendlyName=https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="V7" s="10" t="str">
+        <x:v>https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A8" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1548,14 +1627,13 @@
         <x:v>AUO 董事長，由 CNA 報導</x:v>
       </x:c>
       <x:c r="U8" s="10" t="str">
-        <x:v>分析：先辨識新材料製程使用哪些設備、是否增加電源控制要求，再決定工程投入。零組件轉型可能形成設備需求，現階段未有可量化的 AEIS 訂單或資本支出影響。</x:v>
-      </x:c>
-      <x:c r="V8" s="10" t="e">
-        <x:f>HYPERLINK("https://www.cna.com.tw/news/afe/202610170118.aspx","https://www.cna.com.tw/news/afe/202610170118.aspx")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cna.com.tw/news/afe/202610170118.aspx, friendlyName=https://www.cna.com.tw/news/afe/202610170118.aspx</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="72" hidden="0" customHeight="1">
+        <x:v>分析：先辨識新材料製程使用哪些設備、是否增加電源控制要求，再決定工程投入。零組件轉型可能形成設備需求，現階段未有可量化的 電源供應商 訂單或資本支出影響。</x:v>
+      </x:c>
+      <x:c r="V8" s="10" t="str">
+        <x:v>https://www.cna.com.tw/news/afe/202610170118.aspx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A9" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1605,12 +1683,11 @@
       <x:c r="U9" s="10" t="str">
         <x:v>分析：分別追蹤前段設備電源、封裝設備及 PC 系統電源的可服務範圍。新品上市尚不足以調高供應量，應等待通路售出、企業導入、退貨率與平台毛利。</x:v>
       </x:c>
-      <x:c r="V9" s="10" t="e">
-        <x:f>HYPERLINK("https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs","https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs, friendlyName=https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="V9" s="10" t="str">
+        <x:v>https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A10" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1660,12 +1737,11 @@
       <x:c r="U10" s="10" t="str">
         <x:v>大型客戶在美國蓋廠，只完成供應鏈在地化的一部分。對中小供應商，關鍵是園區能否提供穩定訂單、共用設施與可負擔的資金，而不只是一塊海外土地。</x:v>
       </x:c>
-      <x:c r="V10" s="10" t="e">
-        <x:f>HYPERLINK("https://www.cna.com.tw/news/afe/202610160128.aspx","https://www.cna.com.tw/news/afe/202610160128.aspx")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cna.com.tw/news/afe/202610160128.aspx, friendlyName=https://www.cna.com.tw/news/afe/202610160128.aspx</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="V10" s="10" t="str">
+        <x:v>https://www.cna.com.tw/news/afe/202610160128.aspx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A11" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1715,12 +1791,11 @@
       <x:c r="U11" s="10" t="str">
         <x:v>大型客戶在美國蓋廠，只完成供應鏈在地化的一部分。對中小供應商，關鍵是園區能否提供穩定訂單、共用設施與可負擔的資金，而不只是一塊海外土地。</x:v>
       </x:c>
-      <x:c r="V11" s="10" t="e">
-        <x:f>HYPERLINK("https://www.cna.com.tw/news/afe/202610160128.aspx","https://www.cna.com.tw/news/afe/202610160128.aspx")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cna.com.tw/news/afe/202610160128.aspx, friendlyName=https://www.cna.com.tw/news/afe/202610160128.aspx</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="72" hidden="0" customHeight="1">
+      <x:c r="V11" s="10" t="str">
+        <x:v>https://www.cna.com.tw/news/afe/202610160128.aspx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A12" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1777,12 +1852,11 @@
       <x:c r="U12" s="10" t="str">
         <x:v>這份預測的重點是 AI 硬體需求如何傳到投資與消費。分析時仍要分清：少數出口產業的強勁成長、整體 GDP，以及每個人的收入感受，三者不會等比例變動。</x:v>
       </x:c>
-      <x:c r="V12" s="10" t="e">
-        <x:f>HYPERLINK("https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/","https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/, friendlyName=https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="72" hidden="0" customHeight="1">
+      <x:c r="V12" s="10" t="str">
+        <x:v>https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A13" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1830,43 +1904,42 @@
         <x:v>AIC / KBC，由 TNGlobal 報導</x:v>
       </x:c>
       <x:c r="U13" s="10" t="str">
-        <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 AEIS 收入或投資回收。</x:v>
-      </x:c>
-      <x:c r="V13" s="10" t="e">
-        <x:f>HYPERLINK("https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/","https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/, friendlyName=https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="72" hidden="0" customHeight="1">
+        <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 電源供應商 收入或投資回收。</x:v>
+      </x:c>
+      <x:c r="V13" s="10" t="str">
+        <x:v>https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A14" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B14" s="13" t="d">
-        <x:v>2026-10-16T00:00:00.000Z</x:v>
+        <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>2026-10-17:19</x:v>
+        <x:v>2026-10-17:18</x:v>
       </x:c>
       <x:c r="D14" s="10" t="str">
-        <x:v>馬來西亞；台灣</x:v>
+        <x:v>越南</x:v>
       </x:c>
       <x:c r="E14" s="10" t="str">
-        <x:v>半導體；後段封測；設備服務</x:v>
+        <x:v>AI 資料中心；電源；能源</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
-        <x:v>活動職缺下限</x:v>
+        <x:v>首期規劃容量上限</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>超過此數，非實際聘用</x:v>
+        <x:v>既有規劃，非已通電容量</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
-        <x:v>2026-10-14 至 2026-10-17</x:v>
+        <x:v>首期規劃，投產時程待核實</x:v>
       </x:c>
       <x:c r="I14" s="17" t="n">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
-        <x:v>個職缺</x:v>
+        <x:v>MW</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str"/>
       <x:c r="L14" s="17"/>
@@ -1879,20 +1952,19 @@
       <x:c r="Q14" s="17"/>
       <x:c r="R14" s="18"/>
       <x:c r="S14" s="10" t="str">
-        <x:v>未揭露可比基期；不倒推</x:v>
+        <x:v>未提供可比基期；不倒推</x:v>
       </x:c>
       <x:c r="T14" s="10" t="str">
-        <x:v>主辦活動，由 CNA 報導</x:v>
+        <x:v>AIC / KBC 計畫，由 TNGlobal 報導</x:v>
       </x:c>
       <x:c r="U14" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 AEIS 合作、客戶採購或新的工廠投資。</x:v>
-      </x:c>
-      <x:c r="V14" s="10" t="e">
-        <x:f>HYPERLINK("https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side","https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side, friendlyName=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="72" hidden="0" customHeight="1">
+        <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 電源供應商 收入或投資回收。</x:v>
+      </x:c>
+      <x:c r="V14" s="10" t="str">
+        <x:v>https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A15" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1909,19 +1981,19 @@
         <x:v>半導體；後段封測；設備服務</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
-        <x:v>園區公司數</x:v>
+        <x:v>活動職缺下限</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>官方陳述</x:v>
+        <x:v>超過此數，非實際聘用</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
-        <x:v>2026-10-16 官員說明</x:v>
+        <x:v>2026-10 中旬招募；起日來源有差異</x:v>
       </x:c>
       <x:c r="I15" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
-        <x:v>家</x:v>
+        <x:v>個職缺</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str"/>
       <x:c r="L15" s="17"/>
@@ -1937,17 +2009,16 @@
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
       <x:c r="T15" s="10" t="str">
-        <x:v>雪蘭莪官員，由 CNA 報導</x:v>
+        <x:v>主辦活動，由 CNA 報導</x:v>
       </x:c>
       <x:c r="U15" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 AEIS 合作、客戶採購或新的工廠投資。</x:v>
-      </x:c>
-      <x:c r="V15" s="10" t="e">
-        <x:f>HYPERLINK("https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side","https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side, friendlyName=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="72" hidden="0" customHeight="1">
+        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
+      </x:c>
+      <x:c r="V15" s="10" t="str">
+        <x:v>https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A16" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1964,7 +2035,7 @@
         <x:v>半導體；後段封測；設備服務</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>園區工程師數</x:v>
+        <x:v>園區公司數</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
         <x:v>官方陳述</x:v>
@@ -1973,10 +2044,10 @@
         <x:v>2026-10-16 官員說明</x:v>
       </x:c>
       <x:c r="I16" s="17" t="n">
-        <x:v>409</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>人</x:v>
+        <x:v>家</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str"/>
       <x:c r="L16" s="17"/>
@@ -1995,54 +2066,49 @@
         <x:v>雪蘭莪官員，由 CNA 報導</x:v>
       </x:c>
       <x:c r="U16" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 AEIS 合作、客戶採購或新的工廠投資。</x:v>
-      </x:c>
-      <x:c r="V16" s="10" t="e">
-        <x:f>HYPERLINK("https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side","https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side, friendlyName=https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="72" hidden="0" customHeight="1">
+        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
+      </x:c>
+      <x:c r="V16" s="10" t="str">
+        <x:v>https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A17" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B17" s="13" t="d">
-        <x:v>2026-10-03T00:00:00.000Z</x:v>
+        <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>2026-10-17:20</x:v>
+        <x:v>2026-10-17:19</x:v>
       </x:c>
       <x:c r="D17" s="10" t="str">
-        <x:v>越南；新加坡</x:v>
+        <x:v>馬來西亞；台灣</x:v>
       </x:c>
       <x:c r="E17" s="10" t="str">
-        <x:v>製造業；外商投資；工業電源</x:v>
+        <x:v>半導體；後段封測；設備服務</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
-        <x:v>FDI 實現額估計</x:v>
+        <x:v>園區工程師數</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>官方估計</x:v>
+        <x:v>官方陳述</x:v>
       </x:c>
       <x:c r="H17" s="10" t="str">
-        <x:v>2026-01 至 2026-09</x:v>
+        <x:v>2026-10-16 官員說明</x:v>
       </x:c>
       <x:c r="I17" s="17" t="n">
-        <x:v>21.07</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
-        <x:v>USD billion</x:v>
-      </x:c>
-      <x:c r="K17" s="10" t="str">
-        <x:v>2025-01 至 2025-09</x:v>
-      </x:c>
+        <x:v>人</x:v>
+      </x:c>
+      <x:c r="K17" s="10" t="str"/>
       <x:c r="L17" s="17"/>
       <x:c r="M17" s="10" t="str">
-        <x:v>YoY</x:v>
-      </x:c>
-      <x:c r="N17" s="18" t="n">
-        <x:v>0.121</x:v>
-      </x:c>
+        <x:v>無</x:v>
+      </x:c>
+      <x:c r="N17" s="18"/>
       <x:c r="O17" s="18"/>
       <x:c r="P17" s="17"/>
       <x:c r="Q17" s="17"/>
@@ -2051,79 +2117,297 @@
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
       <x:c r="T17" s="10" t="str">
+        <x:v>雪蘭莪官員，由 CNA 報導</x:v>
+      </x:c>
+      <x:c r="U17" s="10" t="str">
+        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
+      </x:c>
+      <x:c r="V17" s="10" t="str">
+        <x:v>https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="28.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A18" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="d">
+        <x:v>2026-10-16T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
+        <x:v>2026-10-17:19</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="str">
+        <x:v>馬來西亞；台灣</x:v>
+      </x:c>
+      <x:c r="E18" s="10" t="str">
+        <x:v>半導體；後段封測；設備服務</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="str">
+        <x:v>合作計畫規模</x:v>
+      </x:c>
+      <x:c r="G18" s="10" t="str">
+        <x:v>官員陳述的計畫規模，非已實現 FDI</x:v>
+      </x:c>
+      <x:c r="H18" s="10" t="str">
+        <x:v>2026-10-16 官員說明，撥款時程未披露</x:v>
+      </x:c>
+      <x:c r="I18" s="17" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J18" s="10" t="str">
+        <x:v>MYR million</x:v>
+      </x:c>
+      <x:c r="K18" s="10" t="str"/>
+      <x:c r="L18" s="17"/>
+      <x:c r="M18" s="10" t="str">
+        <x:v>無</x:v>
+      </x:c>
+      <x:c r="N18" s="18"/>
+      <x:c r="O18" s="18"/>
+      <x:c r="P18" s="17"/>
+      <x:c r="Q18" s="17"/>
+      <x:c r="R18" s="18"/>
+      <x:c r="S18" s="10" t="str">
+        <x:v>未提供可比基期；不倒推</x:v>
+      </x:c>
+      <x:c r="T18" s="10" t="str">
+        <x:v>雪蘭莪官員，由 CNA 報導</x:v>
+      </x:c>
+      <x:c r="U18" s="10" t="str">
+        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
+      </x:c>
+      <x:c r="V18" s="10" t="str">
+        <x:v>https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="28.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A19" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
+        <x:v>2026-10-17:20</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="str">
+        <x:v>越南；新加坡</x:v>
+      </x:c>
+      <x:c r="E19" s="10" t="str">
+        <x:v>製造業；外商投資；工業電源</x:v>
+      </x:c>
+      <x:c r="F19" s="10" t="str">
+        <x:v>FDI 實現額估計</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="str">
+        <x:v>官方估計</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="str">
+        <x:v>2026-01 至 2026-09</x:v>
+      </x:c>
+      <x:c r="I19" s="17" t="n">
+        <x:v>21.07</x:v>
+      </x:c>
+      <x:c r="J19" s="10" t="str">
+        <x:v>USD billion</x:v>
+      </x:c>
+      <x:c r="K19" s="10" t="str">
+        <x:v>2025-01 至 2025-09</x:v>
+      </x:c>
+      <x:c r="L19" s="17"/>
+      <x:c r="M19" s="10" t="str">
+        <x:v>YoY</x:v>
+      </x:c>
+      <x:c r="N19" s="18" t="n">
+        <x:v>0.121</x:v>
+      </x:c>
+      <x:c r="O19" s="18"/>
+      <x:c r="P19" s="17"/>
+      <x:c r="Q19" s="17"/>
+      <x:c r="R19" s="18"/>
+      <x:c r="S19" s="10" t="str">
+        <x:v>未揭露可比基期；不倒推</x:v>
+      </x:c>
+      <x:c r="T19" s="10" t="str">
         <x:v>越南國家統計局，由政府新聞網公布</x:v>
       </x:c>
-      <x:c r="U17" s="10" t="str">
-        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 AEIS 的成長率。</x:v>
-      </x:c>
-      <x:c r="V17" s="10" t="e">
-        <x:f>HYPERLINK("https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm","https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm, friendlyName=https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="72" hidden="0" customHeight="1">
-      <x:c r="A18" s="14" t="d">
-        <x:v>2026-10-17T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B18" s="14" t="d">
+      <x:c r="U19" s="10" t="str">
+        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
+      </x:c>
+      <x:c r="V19" s="10" t="str">
+        <x:v>https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="28.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A20" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="str">
+      <x:c r="C20" s="10" t="str">
         <x:v>2026-10-17:20</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="str">
+      <x:c r="D20" s="10" t="str">
         <x:v>越南；新加坡</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="str">
+      <x:c r="E20" s="10" t="str">
         <x:v>製造業；外商投資；工業電源</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="str">
+      <x:c r="F20" s="10" t="str">
         <x:v>總註冊外資</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="str">
+      <x:c r="G20" s="10" t="str">
         <x:v>官方統計</x:v>
       </x:c>
-      <x:c r="H18" s="11" t="str">
+      <x:c r="H20" s="10" t="str">
         <x:v>2026-01 至 2026-09</x:v>
       </x:c>
-      <x:c r="I18" s="20" t="n">
+      <x:c r="I20" s="17" t="n">
         <x:v>50.36</x:v>
       </x:c>
-      <x:c r="J18" s="11" t="str">
+      <x:c r="J20" s="10" t="str">
         <x:v>USD billion</x:v>
       </x:c>
-      <x:c r="K18" s="11" t="str">
+      <x:c r="K20" s="10" t="str">
         <x:v>2025-01 至 2025-09</x:v>
       </x:c>
-      <x:c r="L18" s="20"/>
-      <x:c r="M18" s="11" t="str">
+      <x:c r="L20" s="17"/>
+      <x:c r="M20" s="10" t="str">
         <x:v>YoY</x:v>
       </x:c>
-      <x:c r="N18" s="21" t="n">
+      <x:c r="N20" s="18" t="n">
         <x:v>0.764</x:v>
       </x:c>
-      <x:c r="O18" s="21"/>
-      <x:c r="P18" s="20"/>
-      <x:c r="Q18" s="20"/>
-      <x:c r="R18" s="21"/>
-      <x:c r="S18" s="11" t="str">
+      <x:c r="O20" s="18"/>
+      <x:c r="P20" s="17"/>
+      <x:c r="Q20" s="17"/>
+      <x:c r="R20" s="18"/>
+      <x:c r="S20" s="10" t="str">
         <x:v>未揭露可比基期；不倒推</x:v>
       </x:c>
-      <x:c r="T18" s="11" t="str">
+      <x:c r="T20" s="10" t="str">
         <x:v>越南國家統計局，由政府新聞網公布</x:v>
       </x:c>
-      <x:c r="U18" s="11" t="str">
-        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 AEIS 的成長率。</x:v>
-      </x:c>
-      <x:c r="V18" s="11" t="e">
-        <x:f>HYPERLINK("https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm","https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm, friendlyName=https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm</x:v>
+      <x:c r="U20" s="10" t="str">
+        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
+      </x:c>
+      <x:c r="V20" s="10" t="str">
+        <x:v>https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="28.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A21" s="13" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
+        <x:v>2026-10-17:20</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>越南；新加坡</x:v>
+      </x:c>
+      <x:c r="E21" s="10" t="str">
+        <x:v>製造業；外商投資；工業電源</x:v>
+      </x:c>
+      <x:c r="F21" s="10" t="str">
+        <x:v>製造加工業新案與增資</x:v>
+      </x:c>
+      <x:c r="G21" s="10" t="str">
+        <x:v>媒體引述分項，官方原表待核對</x:v>
+      </x:c>
+      <x:c r="H21" s="10" t="str">
+        <x:v>2026-01 至 2026-09</x:v>
+      </x:c>
+      <x:c r="I21" s="17" t="n">
+        <x:v>21.82</x:v>
+      </x:c>
+      <x:c r="J21" s="10" t="str">
+        <x:v>USD billion</x:v>
+      </x:c>
+      <x:c r="K21" s="10" t="str"/>
+      <x:c r="L21" s="17"/>
+      <x:c r="M21" s="10" t="str">
+        <x:v>無</x:v>
+      </x:c>
+      <x:c r="N21" s="18"/>
+      <x:c r="O21" s="18"/>
+      <x:c r="P21" s="17"/>
+      <x:c r="Q21" s="17"/>
+      <x:c r="R21" s="18"/>
+      <x:c r="S21" s="10" t="str">
+        <x:v>未提供可比基期；不倒推</x:v>
+      </x:c>
+      <x:c r="T21" s="10" t="str">
+        <x:v>越南統計資料，由 VnEconomy 轉述</x:v>
+      </x:c>
+      <x:c r="U21" s="10" t="str">
+        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
+      </x:c>
+      <x:c r="V21" s="10" t="str">
+        <x:v>https://en.vneconomy.vn/vietnams-fdi-attraction-reaches-5036bln-in-9m.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="28.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A22" s="14" t="d">
+        <x:v>2026-10-17T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="str">
+        <x:v>2026-10-17:20</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="str">
+        <x:v>越南；新加坡</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="str">
+        <x:v>製造業；外商投資；工業電源</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="str">
+        <x:v>新加坡來源的新註冊資本</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="str">
+        <x:v>媒體引述分項，官方原表待核對</x:v>
+      </x:c>
+      <x:c r="H22" s="11" t="str">
+        <x:v>2026-01 至 2026-09</x:v>
+      </x:c>
+      <x:c r="I22" s="20" t="n">
+        <x:v>9.26</x:v>
+      </x:c>
+      <x:c r="J22" s="11" t="str">
+        <x:v>USD billion</x:v>
+      </x:c>
+      <x:c r="K22" s="11" t="str"/>
+      <x:c r="L22" s="20"/>
+      <x:c r="M22" s="11" t="str">
+        <x:v>無</x:v>
+      </x:c>
+      <x:c r="N22" s="21"/>
+      <x:c r="O22" s="21"/>
+      <x:c r="P22" s="20"/>
+      <x:c r="Q22" s="20"/>
+      <x:c r="R22" s="21"/>
+      <x:c r="S22" s="11" t="str">
+        <x:v>未提供可比基期；不倒推</x:v>
+      </x:c>
+      <x:c r="T22" s="11" t="str">
+        <x:v>越南統計資料，由 VnEconomy 轉述</x:v>
+      </x:c>
+      <x:c r="U22" s="11" t="str">
+        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
+      </x:c>
+      <x:c r="V22" s="11" t="str">
+        <x:v>https://en.vneconomy.vn/vietnams-fdi-attraction-reaches-5036bln-in-9m.htm</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c62177345ab4e9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b6c4bef19564039"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2152,7 +2436,7 @@
         <x:v>閱讀角度</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>Advanced Energy Industries (NASDAQ: AEIS)。半導體設備精密電源、資料中心電源、工業客戶與區域服務；影響為編輯分析。</x:v>
+        <x:v>從半導體設備、電源、資料中心與工業供應鏈的經營決策評估市場；影響判斷為編輯分析。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -2229,10 +2513,10 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="10" t="str">
-        <x:v>AEIS 影響</x:v>
+        <x:v>營運影響</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>來源沒有披露 AEIS 訂單或影響金額時保持未知，不以市場增幅直接推算公司收入。</x:v>
+        <x:v>未披露的訂單或影響金額保持未知，不以市場增幅直接推算個別公司的收入。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -2243,20 +2527,20 @@
         <x:v>CoWoS 與美光屬本週追蹤；越南 FDI 於 10/3 發布，非今日新統計。</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="57.599998474121094" hidden="0" customHeight="1">
+    <x:row r="14" ht="72" hidden="0" customHeight="1">
       <x:c r="A14" s="10" t="str">
         <x:v>來源限制</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>本期聚焦台灣與東南亞，更新至台北時間 10 月 17 日晚間。CoWoS、美光及越南 10 月 3 日 FDI 資料明列為本週追蹤或區域背景。展示規格、友達目標、園區估算與 GDP 預測均非實際訂單。友達及馬來西亞園區數字依具名採訪；胡志明市電價依專業報導，未取得原始會議文件或最終費率，屬來源受限。AEIS 影響評估為編輯分析，未披露的訂單與金額保持未知。Excel 缺少基期時保留空白及原因，YoY 與百分點分開。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="28.799999237060547" hidden="0" customHeight="1">
+        <x:v>本期聚焦台灣與東南亞。CoWoS、美光、10 月 14 日工廠 AI 合作及越南 10 月 3 日 FDI 資料明列為追蹤或背景。展示規格、公司目標、園區估算與 GDP 預測均非已完成訂單。友達與馬來西亞園區數字依具名採訪；胡志明市電價缺原始會議文件及最終費率，越南製造業及資金來源分項未核對官方原表，這些部分屬來源受限。營運影響與情境推演為編輯分析，未披露的訂單、基期與影響金額保持未知。 活動地點依主辦資料補充；MSRD 招募起日存在 10/14 與 10/15 兩種主辦頁記載，KLCC 場館則一致。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="10" t="str">
-        <x:v>AEIS 業務背景</x:v>
+        <x:v>地點判讀</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>https://ir.advancedenergy.com/media/document/fcbde7e4-483b-4dcc-93cc-985a436746b5/assets/2026-09_AEIS_IR_Presentation.pdf</x:v>
+        <x:v>活動場館、企業所在地與投資案址分開記錄。未核實的場館保持未知，不以公司總部代替。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -2264,13 +2548,13 @@
         <x:v>資料更新</x:v>
       </x:c>
       <x:c r="B16" s="11" t="d">
-        <x:v>2026-10-17T10:45:57.185Z</x:v>
+        <x:v>2026-10-17T11:34:06.828Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb93ff0d991ad4052"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95ec172c6d644ddd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="市場動向" sheetId="1" r:id="Ree6ca0fc10854099"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="數值明細" sheetId="2" r:id="Rd15165484d5f4a9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位說明" sheetId="3" r:id="R422d59829d4044f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="市場動向" sheetId="1" r:id="R72f3ccba992b4289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="數值明細" sheetId="2" r:id="R64de6787772c40d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位說明" sheetId="3" r:id="R7194c99e7fef40e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -182,11 +182,11 @@
     <x:tableColumn id="9" name="外商投資 FDI"/>
     <x:tableColumn id="10" name="標題"/>
     <x:tableColumn id="11" name="事件摘要"/>
-    <x:tableColumn id="12" name="業務關聯"/>
-    <x:tableColumn id="13" name="影響評估（分析）"/>
-    <x:tableColumn id="14" name="影響時程"/>
-    <x:tableColumn id="15" name="建議檢查事項"/>
-    <x:tableColumn id="16" name="下一驗證點"/>
+    <x:tableColumn id="12" name="產業關聯"/>
+    <x:tableColumn id="13" name="影響評估（自行填寫）"/>
+    <x:tableColumn id="14" name="已公布時程"/>
+    <x:tableColumn id="15" name="分析備註（自行填寫）"/>
+    <x:tableColumn id="16" name="待確認事項"/>
     <x:tableColumn id="17" name="查證信心"/>
     <x:tableColumn id="18" name="來源類型"/>
     <x:tableColumn id="19" name="完整來源與日報連結"/>
@@ -220,7 +220,7 @@
     <x:tableColumn id="18" name="計算變動率"/>
     <x:tableColumn id="19" name="基期與計算說明"/>
     <x:tableColumn id="20" name="數字歸屬"/>
-    <x:tableColumn id="21" name="營運影響評估（分析）"/>
+    <x:tableColumn id="21" name="影響評估（自行填寫）"/>
     <x:tableColumn id="22" name="來源連結"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -493,19 +493,19 @@
         <x:v>事件摘要</x:v>
       </x:c>
       <x:c r="L1" s="7" t="str">
-        <x:v>業務關聯</x:v>
+        <x:v>產業關聯</x:v>
       </x:c>
       <x:c r="M1" s="7" t="str">
-        <x:v>影響評估（分析）</x:v>
+        <x:v>影響評估（自行填寫）</x:v>
       </x:c>
       <x:c r="N1" s="7" t="str">
-        <x:v>影響時程</x:v>
+        <x:v>已公布時程</x:v>
       </x:c>
       <x:c r="O1" s="7" t="str">
-        <x:v>建議檢查事項</x:v>
+        <x:v>分析備註（自行填寫）</x:v>
       </x:c>
       <x:c r="P1" s="7" t="str">
-        <x:v>下一驗證點</x:v>
+        <x:v>待確認事項</x:v>
       </x:c>
       <x:c r="Q1" s="7" t="str">
         <x:v>查證信心</x:v>
@@ -549,25 +549,21 @@
         <x:v>美商在台廠房開幕，新增金額未披露</x:v>
       </x:c>
       <x:c r="J2" s="9" t="str">
-        <x:v>本週追蹤：AI 晶片供給要同時看 CoWoS、HBM 與後段測試</x:v>
+        <x:v>本週追蹤：台積電 CoWoS 量產與美光台中 HBM 封裝測試廠啟用</x:v>
       </x:c>
       <x:c r="K2" s="9" t="str">
         <x:v>台積電 10 月 15 日法說表示，5 倍光罩尺寸的 CoWoS 已量產；同日美光台中 AATT2 先進封裝測試廠開幕，支援 HBM。這兩項是本週進展，今日整合追蹤，並無新增產能數字。</x:v>
       </x:c>
       <x:c r="L2" s="9" t="str">
-        <x:v>半導體設備精密電源，間接需求</x:v>
-      </x:c>
-      <x:c r="M2" s="9" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
-      </x:c>
+        <x:v>晶圓製造、HBM 與先進封裝測試</x:v>
+      </x:c>
+      <x:c r="M2" s="9" t="str"/>
       <x:c r="N2" s="9" t="str">
-        <x:v>近期認證與中期設備拉貨</x:v>
-      </x:c>
-      <x:c r="O2" s="9" t="str">
-        <x:v>確認設備客戶認證及備料節奏</x:v>
-      </x:c>
+        <x:v>10 月 15 日法說及開幕；量產產出未完整披露</x:v>
+      </x:c>
+      <x:c r="O2" s="9" t="str"/>
       <x:c r="P2" s="9" t="str">
-        <x:v>實際產能、良率、利用率與設備訂單</x:v>
+        <x:v>AATT2 新增 HBM 產出、設備訂單及個別供應商營收未披露</x:v>
       </x:c>
       <x:c r="Q2" s="9" t="str">
         <x:v>高</x:v>
@@ -611,25 +607,21 @@
         <x:v>未披露外商投資金額</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>OCP 台廠展示整機櫃、800 VDC 電源與液冷，量產驗收成為下一關</x:v>
+        <x:v>台廠於聖荷西 OCP 展示整機櫃、800 VDC 電源與液冷</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
         <x:v>中央社 10 月 17 日整理 10 月 12 至 15 日於美國加州聖荷西舉辦的 OCP 展會：緯穎、華碩與勤誠等展示下一代伺服器或機櫃，台達電、光寶與康舒展示高壓直流電源及相關方案。台達電 10 月 15 日公司稿列出 800 VDC 電源櫃、備援與液冷產品，展示規格仍需與量產部署分開。</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>資料中心電源直接相關，未證實 電源供應商 新訂單</x:v>
-      </x:c>
-      <x:c r="M3" s="10" t="str">
-        <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
-      </x:c>
+        <x:v>機櫃、電源、備援與液冷產品</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str"/>
       <x:c r="N3" s="10" t="str">
-        <x:v>依客戶認證及量產時程</x:v>
-      </x:c>
-      <x:c r="O3" s="10" t="str">
-        <x:v>比較系統整合、效率與服務條件</x:v>
-      </x:c>
+        <x:v>展期 10 月 12 至 15 日；各產品量產時程依廠商披露</x:v>
+      </x:c>
+      <x:c r="O3" s="10" t="str"/>
       <x:c r="P3" s="10" t="str">
-        <x:v>認證、量產訂單與每櫃電源價值</x:v>
+        <x:v>同口徑售價、成本、客戶訂單及實際部署量未披露</x:v>
       </x:c>
       <x:c r="Q3" s="10" t="str">
         <x:v>高</x:v>
@@ -679,19 +671,15 @@
         <x:v>友達董事長彭双浪 10 月 17 日表示，公司在先進封裝將扮演零組件供應者，運用玻璃與 TGV 技術；與康寧合作的技術已有低軌衛星天線應用。MicroLED 光通訊與 CPO 的量產時間估計仍為兩至三年，屬公司展望。</x:v>
       </x:c>
       <x:c r="L4" s="10" t="str">
-        <x:v>新材料設備電源的潛在需求</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>分析：先辨識新材料製程使用哪些設備、是否增加電源控制要求，再決定工程投入。零組件轉型可能形成設備需求，現階段未有可量化的 電源供應商 訂單或資本支出影響。</x:v>
-      </x:c>
+        <x:v>玻璃基板、TGV 與光通訊零組件</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="str"/>
       <x:c r="N4" s="10" t="str">
-        <x:v>光通訊量產展望兩至三年，屬公司估計</x:v>
-      </x:c>
-      <x:c r="O4" s="10" t="str">
-        <x:v>先確認製程與可服務設備</x:v>
-      </x:c>
+        <x:v>2030 年營收組合目標；光通訊量產估兩至三年</x:v>
+      </x:c>
+      <x:c r="O4" s="10" t="str"/>
       <x:c r="P4" s="10" t="str">
-        <x:v>客戶認證、量產良率與新業務收入</x:v>
+        <x:v>新業務獲利、客戶認證及完整逐字稿尚未取得</x:v>
       </x:c>
       <x:c r="Q4" s="10" t="str">
         <x:v>中</x:v>
@@ -741,19 +729,15 @@
         <x:v>NVIDIA 10 月 16 日宣布 RTX Spark Windows 電腦上市，品牌包括華碩、微星及多家國際 PC 廠，採 Grace CPU 與 Blackwell GPU。公司主管向中央社說明聯發科參與 CPU 設計，並使用 CoWoS 封裝；需求與產能判斷仍屬公司說法。</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str">
-        <x:v>PC 電源與製程電源機會需分開</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="str">
-        <x:v>分析：分別追蹤前段設備電源、封裝設備及 PC 系統電源的可服務範圍。新品上市尚不足以調高供應量，應等待通路售出、企業導入、退貨率與平台毛利。</x:v>
-      </x:c>
+        <x:v>本地 AI 電腦、晶片設計與封裝</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str"/>
       <x:c r="N5" s="10" t="str">
-        <x:v>新品上市後數季</x:v>
-      </x:c>
-      <x:c r="O5" s="10" t="str">
-        <x:v>等待售出與企業導入，再調整供應</x:v>
-      </x:c>
+        <x:v>10 月 16 日宣布上市</x:v>
+      </x:c>
+      <x:c r="O5" s="10" t="str"/>
       <x:c r="P5" s="10" t="str">
-        <x:v>出貨、使用率、能耗與退貨率</x:v>
+        <x:v>本期未取得出貨、使用率及完整生命週期成本</x:v>
       </x:c>
       <x:c r="Q5" s="10" t="str">
         <x:v>高</x:v>
@@ -803,19 +787,15 @@
         <x:v>經濟部 10 月 16 日向中央社說明，將與電電公會推動海外產業園區，採業者出資、政府協助模式。龔明鑫專訪提及由德州起步、規劃不只一座；單一園區 20 億至 40 億美元是估算，土地取得細節尚未對外確認。</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str">
-        <x:v>在地服務、庫存與製造成本</x:v>
-      </x:c>
-      <x:c r="M6" s="10" t="str">
-        <x:v>大型客戶在美國蓋廠，只完成供應鏈在地化的一部分。對中小供應商，關鍵是園區能否提供穩定訂單、共用設施與可負擔的資金，而不只是一塊海外土地。</x:v>
-      </x:c>
+        <x:v>海外產業園區與台灣零組件供應鏈</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="str"/>
       <x:c r="N6" s="10" t="str">
-        <x:v>用地及融資確定後</x:v>
-      </x:c>
-      <x:c r="O6" s="10" t="str">
-        <x:v>以已簽需求檢查布局</x:v>
-      </x:c>
+        <x:v>10 月 16 日說明；土地及動工時程未確認</x:v>
+      </x:c>
+      <x:c r="O6" s="10" t="str"/>
       <x:c r="P6" s="10" t="str">
-        <x:v>融資、土地、入駐名單與動工</x:v>
+        <x:v>開發主體、用地、完整融資及入駐名單尚未確認</x:v>
       </x:c>
       <x:c r="Q6" s="10" t="str">
         <x:v>中</x:v>
@@ -865,19 +845,15 @@
         <x:v>中經院 10 月 16 日公布第四季預測，把 2026 年經濟成長率由 7 月的 10.35% 上修至 12.16%，提高 1.81 個百分點。預估內需貢獻 6.63 個百分點、國外淨需求貢獻 5.53 個百分點；全年數字仍是預測。</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str">
-        <x:v>客戶資本支出與區域服務規劃</x:v>
-      </x:c>
-      <x:c r="M7" s="10" t="str">
-        <x:v>這份預測的重點是 AI 硬體需求如何傳到投資與消費。分析時仍要分清：少數出口產業的強勁成長、整體 GDP，以及每個人的收入感受，三者不會等比例變動。</x:v>
-      </x:c>
+        <x:v>台灣總體經濟及投資、出口統計背景</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="str"/>
       <x:c r="N7" s="10" t="str">
-        <x:v>2026 年全年預測</x:v>
-      </x:c>
-      <x:c r="O7" s="10" t="str">
-        <x:v>用設備客戶訂單驗證總體展望</x:v>
-      </x:c>
+        <x:v>10 月 16 日公布 2026 年第四季預測</x:v>
+      </x:c>
+      <x:c r="O7" s="10" t="str"/>
       <x:c r="P7" s="10" t="str">
-        <x:v>GDP 實績、民間投資與客戶拉貨</x:v>
+        <x:v>全年 GDP 尚為預測，後續實績可能修訂</x:v>
       </x:c>
       <x:c r="Q7" s="10" t="str">
         <x:v>高</x:v>
@@ -927,19 +903,15 @@
         <x:v>TNGlobal 10 月 16 日報導，胡志明市工業區管理機關在 10 月 15 日經濟會議要求統一 AI 資料中心電價指引。所涉 AIC 與 KBC 計畫早於 3 月公布，總規劃金額 21 億美元；本次新增進展是電價問題，並非新宣布投資。</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>資料中心電源，部署時點風險</x:v>
-      </x:c>
-      <x:c r="M8" s="10" t="str">
-        <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 電源供應商 收入或投資回收。</x:v>
-      </x:c>
+        <x:v>資料中心電力與越南工業區</x:v>
+      </x:c>
+      <x:c r="M8" s="10" t="str"/>
       <x:c r="N8" s="10" t="str">
-        <x:v>待費率分類與電力合約</x:v>
-      </x:c>
-      <x:c r="O8" s="10" t="str">
-        <x:v>確認電力條件再排工程及交貨</x:v>
-      </x:c>
+        <x:v>10 月 15 日會議、10 月 16 日報導；最終費率未定</x:v>
+      </x:c>
+      <x:c r="O8" s="10" t="str"/>
       <x:c r="P8" s="10" t="str">
-        <x:v>正式費率、融資與上線</x:v>
+        <x:v>原始會議文件、最終費率、用電曲線與電力合約未取得</x:v>
       </x:c>
       <x:c r="Q8" s="10" t="str">
         <x:v>中</x:v>
@@ -989,19 +961,15 @@
         <x:v>中央社 10 月 16 日報導，雪蘭莪相關機構在吉隆坡會展中心（KLCC）主辦的半導體招募活動提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備及廠務。官員表示兩座 IC 設計園區有 20 家公司、409 名工程師，與檳城製造、組裝測試形成互補。</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str">
-        <x:v>區域服務與工程人才，間接相關</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
-      </x:c>
+        <x:v>IC 設計、製程、設備、廠務與封測人才</x:v>
+      </x:c>
+      <x:c r="M9" s="10" t="str"/>
       <x:c r="N9" s="10" t="str">
-        <x:v>當期招募與後續認證</x:v>
-      </x:c>
-      <x:c r="O9" s="10" t="str">
-        <x:v>檢查客戶密度、人才與維修週轉</x:v>
-      </x:c>
+        <x:v>10 月中旬招募；主辦頁起日為 10/14 或 10/15</x:v>
+      </x:c>
+      <x:c r="O9" s="10" t="str"/>
       <x:c r="P9" s="10" t="str">
-        <x:v>聘用、留任與客戶設備認證</x:v>
+        <x:v>實際聘用與留任未披露；園區及計畫數字依官員陳述</x:v>
       </x:c>
       <x:c r="Q9" s="10" t="str">
         <x:v>中</x:v>
@@ -1051,19 +1019,15 @@
         <x:v>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>在地工業電源與服務的背景指標</x:v>
-      </x:c>
-      <x:c r="M10" s="10" t="str">
-        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
-      </x:c>
+        <x:v>越南製造業投資及外資流量背景</x:v>
+      </x:c>
+      <x:c r="M10" s="10" t="str"/>
       <x:c r="N10" s="10" t="str">
-        <x:v>截至 2026 年 9 月的區域背景</x:v>
-      </x:c>
-      <x:c r="O10" s="10" t="str">
-        <x:v>對到具名廠房與設備採購</x:v>
-      </x:c>
+        <x:v>統計截至 9 月 30 日，10 月 3 日發布</x:v>
+      </x:c>
+      <x:c r="O10" s="10" t="str"/>
       <x:c r="P10" s="10" t="str">
-        <x:v>製造業分項、電網接入與驗收</x:v>
+        <x:v>製造業及資金來源分項未核對官方原表；實現額屬估計</x:v>
       </x:c>
       <x:c r="Q10" s="10" t="str">
         <x:v>中：總量有官方來源，新增分項待核對原表</x:v>
@@ -1107,25 +1071,21 @@
         <x:v>未揭露</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str">
-        <x:v>背景追蹤：工廠 AI 合作延伸到檢測、測試與數位分身，收益仍待驗收</x:v>
+        <x:v>背景追蹤：NVIDIA 公布半導體檢測、測試與工廠 AI 合作</x:v>
       </x:c>
       <x:c r="K11" s="11" t="str">
         <x:v>NVIDIA 10 月 14 日公司稿列出 KLA 檢測、Advantest 測試，以及鴻海、FANUC 等工廠 AI 合作。本期把它作為台灣供應鏈與終端工廠的背景追蹤；各場域地點、全面量產時程與全廠投資報酬未完整公開。</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>工業設備、製程控制及售後服務</x:v>
-      </x:c>
-      <x:c r="M11" s="11" t="str">
-        <x:v>分析：設備與軟體能否改善單一工序，和整廠能否增加可交付產出，是兩個驗收問題。採購前應建立基期，追到良率、停機、返工及現金回收。</x:v>
-      </x:c>
+        <x:v>檢測、測試設備與工廠 AI 軟硬體合作</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="str"/>
       <x:c r="N11" s="11" t="str">
-        <x:v>試點至量產驗收，時程未完整公開</x:v>
-      </x:c>
-      <x:c r="O11" s="11" t="str">
-        <x:v>先建立基期，再看良品成本與現金回收</x:v>
-      </x:c>
+        <x:v>10 月 14 日公司發布；全面部署時程未完整公開</x:v>
+      </x:c>
+      <x:c r="O11" s="11" t="str"/>
       <x:c r="P11" s="11" t="str">
-        <x:v>具名工廠、同條件數據、驗收與維護成本</x:v>
+        <x:v>具名部署廠址、合約計價與量化全廠收益未完整公開</x:v>
       </x:c>
       <x:c r="Q11" s="11" t="str">
         <x:v>中</x:v>
@@ -1143,7 +1103,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf53f71e68ad1478e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04b8ccfbbe494158"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1241,13 +1201,13 @@
         <x:v>數字歸屬</x:v>
       </x:c>
       <x:c r="U1" s="7" t="str">
-        <x:v>營運影響評估（分析）</x:v>
+        <x:v>影響評估（自行填寫）</x:v>
       </x:c>
       <x:c r="V1" s="7" t="str">
         <x:v>來源連結</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="2" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1298,14 +1258,12 @@
       <x:c r="T2" s="9" t="str">
         <x:v>TSMC</x:v>
       </x:c>
-      <x:c r="U2" s="9" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
-      </x:c>
+      <x:c r="U2" s="9" t="str"/>
       <x:c r="V2" s="9" t="str">
         <x:v>https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="3" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A3" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1356,14 +1314,12 @@
       <x:c r="T3" s="10" t="str">
         <x:v>TSMC</x:v>
       </x:c>
-      <x:c r="U3" s="10" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
-      </x:c>
+      <x:c r="U3" s="10" t="str"/>
       <x:c r="V3" s="10" t="str">
         <x:v>https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="4" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A4" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1410,14 +1366,12 @@
       <x:c r="T4" s="10" t="str">
         <x:v>TSMC</x:v>
       </x:c>
-      <x:c r="U4" s="10" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
-      </x:c>
+      <x:c r="U4" s="10" t="str"/>
       <x:c r="V4" s="10" t="str">
         <x:v>https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="5" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A5" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1464,9 +1418,7 @@
       <x:c r="T5" s="10" t="str">
         <x:v>TSMC</x:v>
       </x:c>
-      <x:c r="U5" s="10" t="str">
-        <x:v>分析：優先向設備客戶確認先進邏輯與記憶體新增設備的認證、拉貨時間及每台設備電源含量，再決定產能與備料。HBM 封裝廠開幕本身，無法證明 電源供應商 獲單或收入增加。</x:v>
-      </x:c>
+      <x:c r="U5" s="10" t="str"/>
       <x:c r="V5" s="10" t="str">
         <x:v>https://investor.tsmc.com/english/encrypt/files/encrypt_file/reports/2026-10/526b65af7305df2dde6b9ece6812b1fdf1e49f9b/3Q26%20EarningsRelease.pdf</x:v>
       </x:c>
@@ -1518,9 +1470,7 @@
       <x:c r="T6" s="10" t="str">
         <x:v>Delta</x:v>
       </x:c>
-      <x:c r="U6" s="10" t="str">
-        <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
-      </x:c>
+      <x:c r="U6" s="10" t="str"/>
       <x:c r="V6" s="10" t="str">
         <x:v>https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html</x:v>
       </x:c>
@@ -1572,14 +1522,12 @@
       <x:c r="T7" s="10" t="str">
         <x:v>Delta</x:v>
       </x:c>
-      <x:c r="U7" s="10" t="str">
-        <x:v>分析：應由雲端與 ODM 的認證時程往回排工程資源，確認功率密度、效率、可靠度、備援及供應責任。投資評估需要每櫃電源價值、量產毛利與營運資金，現有公告沒有這些可計算資料。</x:v>
-      </x:c>
+      <x:c r="U7" s="10" t="str"/>
       <x:c r="V7" s="10" t="str">
         <x:v>https://www.prnewswire.com/news-releases/delta-highlights-collaboration-with-nvidia-in-advancing-energy-efficient-800-vdc-power-and-cooling-solutions-for-ai-data-centers-at-ocp-global-summit-2026-302909912.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="28.799999237060547" hidden="0" customHeight="1">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1626,14 +1574,12 @@
       <x:c r="T8" s="10" t="str">
         <x:v>AUO 董事長，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U8" s="10" t="str">
-        <x:v>分析：先辨識新材料製程使用哪些設備、是否增加電源控制要求，再決定工程投入。零組件轉型可能形成設備需求，現階段未有可量化的 電源供應商 訂單或資本支出影響。</x:v>
-      </x:c>
+      <x:c r="U8" s="10" t="str"/>
       <x:c r="V8" s="10" t="str">
         <x:v>https://www.cna.com.tw/news/afe/202610170118.aspx</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="9" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A9" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1680,14 +1626,12 @@
       <x:c r="T9" s="10" t="str">
         <x:v>NVIDIA</x:v>
       </x:c>
-      <x:c r="U9" s="10" t="str">
-        <x:v>分析：分別追蹤前段設備電源、封裝設備及 PC 系統電源的可服務範圍。新品上市尚不足以調高供應量，應等待通路售出、企業導入、退貨率與平台毛利。</x:v>
-      </x:c>
+      <x:c r="U9" s="10" t="str"/>
       <x:c r="V9" s="10" t="str">
         <x:v>https://nvidianews.nvidia.com/news/nvidia-rtx-spark-pcs-available-today-a-new-beginning-for-windows-pcs</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="28.799999237060547" hidden="0" customHeight="1">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1734,14 +1678,12 @@
       <x:c r="T10" s="10" t="str">
         <x:v>經濟部，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U10" s="10" t="str">
-        <x:v>大型客戶在美國蓋廠，只完成供應鏈在地化的一部分。對中小供應商，關鍵是園區能否提供穩定訂單、共用設施與可負擔的資金，而不只是一塊海外土地。</x:v>
-      </x:c>
+      <x:c r="U10" s="10" t="str"/>
       <x:c r="V10" s="10" t="str">
         <x:v>https://www.cna.com.tw/news/afe/202610160128.aspx</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="28.799999237060547" hidden="0" customHeight="1">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1788,14 +1730,12 @@
       <x:c r="T11" s="10" t="str">
         <x:v>經濟部，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U11" s="10" t="str">
-        <x:v>大型客戶在美國蓋廠，只完成供應鏈在地化的一部分。對中小供應商，關鍵是園區能否提供穩定訂單、共用設施與可負擔的資金，而不只是一塊海外土地。</x:v>
-      </x:c>
+      <x:c r="U11" s="10" t="str"/>
       <x:c r="V11" s="10" t="str">
         <x:v>https://www.cna.com.tw/news/afe/202610160128.aspx</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="12" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A12" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -1849,9 +1789,7 @@
       <x:c r="T12" s="10" t="str">
         <x:v>CIER</x:v>
       </x:c>
-      <x:c r="U12" s="10" t="str">
-        <x:v>這份預測的重點是 AI 硬體需求如何傳到投資與消費。分析時仍要分清：少數出口產業的強勁成長、整體 GDP，以及每個人的收入感受，三者不會等比例變動。</x:v>
-      </x:c>
+      <x:c r="U12" s="10" t="str"/>
       <x:c r="V12" s="10" t="str">
         <x:v>https://www.cier.edu.tw/eco/2026%E5%B9%B4%E7%AC%AC4%E5%AD%A3%E8%87%BA%E7%81%A3%E7%B6%93%E6%BF%9F%E9%A0%90%E6%B8%AC/</x:v>
       </x:c>
@@ -1903,9 +1841,7 @@
       <x:c r="T13" s="10" t="str">
         <x:v>AIC / KBC，由 TNGlobal 報導</x:v>
       </x:c>
-      <x:c r="U13" s="10" t="str">
-        <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 電源供應商 收入或投資回收。</x:v>
-      </x:c>
+      <x:c r="U13" s="10" t="str"/>
       <x:c r="V13" s="10" t="str">
         <x:v>https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/</x:v>
       </x:c>
@@ -1957,14 +1893,12 @@
       <x:c r="T14" s="10" t="str">
         <x:v>AIC / KBC 計畫，由 TNGlobal 報導</x:v>
       </x:c>
-      <x:c r="U14" s="10" t="str">
-        <x:v>分析：先確認客戶取得的電力條件，再安排機櫃電源工程與交貨。節能、功率密度及可靠度仍有價值，但現有資料不足以估算 電源供應商 收入或投資回收。</x:v>
-      </x:c>
+      <x:c r="U14" s="10" t="str"/>
       <x:c r="V14" s="10" t="str">
         <x:v>https://technode.global/2026/10/16/hcmc-seeks-clarification-on-power-price-for-2-1b-ai-data-center/</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="28.799999237060547" hidden="0" customHeight="1">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -2011,14 +1945,12 @@
       <x:c r="T15" s="10" t="str">
         <x:v>主辦活動，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U15" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
-      </x:c>
+      <x:c r="U15" s="10" t="str"/>
       <x:c r="V15" s="10" t="str">
         <x:v>https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="28.799999237060547" hidden="0" customHeight="1">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -2065,14 +1997,12 @@
       <x:c r="T16" s="10" t="str">
         <x:v>雪蘭莪官員，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U16" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
-      </x:c>
+      <x:c r="U16" s="10" t="str"/>
       <x:c r="V16" s="10" t="str">
         <x:v>https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="28.799999237060547" hidden="0" customHeight="1">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="13" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
@@ -2119,9 +2049,7 @@
       <x:c r="T17" s="10" t="str">
         <x:v>雪蘭莪官員，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U17" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
-      </x:c>
+      <x:c r="U17" s="10" t="str"/>
       <x:c r="V17" s="10" t="str">
         <x:v>https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
       </x:c>
@@ -2173,9 +2101,7 @@
       <x:c r="T18" s="10" t="str">
         <x:v>雪蘭莪官員，由 CNA 報導</x:v>
       </x:c>
-      <x:c r="U18" s="10" t="str">
-        <x:v>分析：區域服務布局應同時評估客戶密度、現場工程人才與維修週轉時間。台馬培訓合作值得追蹤，但本期沒有確認 電源供應商 合作、客戶採購或新的工廠投資。</x:v>
-      </x:c>
+      <x:c r="U18" s="10" t="str"/>
       <x:c r="V18" s="10" t="str">
         <x:v>https://money.udn.com/money/story/5599/9819018?from=edn_newestlist_cate_side</x:v>
       </x:c>
@@ -2231,9 +2157,7 @@
       <x:c r="T19" s="10" t="str">
         <x:v>越南國家統計局，由政府新聞網公布</x:v>
       </x:c>
-      <x:c r="U19" s="10" t="str">
-        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
-      </x:c>
+      <x:c r="U19" s="10" t="str"/>
       <x:c r="V19" s="10" t="str">
         <x:v>https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm</x:v>
       </x:c>
@@ -2289,9 +2213,7 @@
       <x:c r="T20" s="10" t="str">
         <x:v>越南國家統計局，由政府新聞網公布</x:v>
       </x:c>
-      <x:c r="U20" s="10" t="str">
-        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
-      </x:c>
+      <x:c r="U20" s="10" t="str"/>
       <x:c r="V20" s="10" t="str">
         <x:v>https://en.baochinhphu.vn/viet-nams-gdp-growth-accelerates-to-995-in-q3-111261003093646463.htm</x:v>
       </x:c>
@@ -2343,9 +2265,7 @@
       <x:c r="T21" s="10" t="str">
         <x:v>越南統計資料，由 VnEconomy 轉述</x:v>
       </x:c>
-      <x:c r="U21" s="10" t="str">
-        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
-      </x:c>
+      <x:c r="U21" s="10" t="str"/>
       <x:c r="V21" s="10" t="str">
         <x:v>https://en.vneconomy.vn/vietnams-fdi-attraction-reaches-5036bln-in-9m.htm</x:v>
       </x:c>
@@ -2397,9 +2317,7 @@
       <x:c r="T22" s="11" t="str">
         <x:v>越南統計資料，由 VnEconomy 轉述</x:v>
       </x:c>
-      <x:c r="U22" s="11" t="str">
-        <x:v>分析：先把投資案對到具名工廠、設備進口、電網接入與驗收，再估在地工業電源及維修需求。全國 FDI 只能提供市場背景，無法直接推成半導體設備或 電源供應商 的成長率。</x:v>
-      </x:c>
+      <x:c r="U22" s="11" t="str"/>
       <x:c r="V22" s="11" t="str">
         <x:v>https://en.vneconomy.vn/vietnams-fdi-attraction-reaches-5036bln-in-9m.htm</x:v>
       </x:c>
@@ -2407,7 +2325,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b6c4bef19564039"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc10be2faefcb4669"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2433,10 +2351,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>閱讀角度</x:v>
+        <x:v>涵蓋範圍</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>從半導體設備、電源、資料中心與工業供應鏈的經營決策評估市場；影響判斷為編輯分析。</x:v>
+        <x:v>半導體設備、精密電源、資料中心與工業上下游供應鏈。內容整理已公布事實、數據、來源及資料缺口。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -2513,10 +2431,10 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="10" t="str">
-        <x:v>營運影響</x:v>
+        <x:v>自行分析</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>未披露的訂單或影響金額保持未知，不以市場增幅直接推算個別公司的收入。</x:v>
+        <x:v>影響評估與分析備註欄留白，由讀者填寫。未披露的訂單或影響金額保持未知。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -2532,7 +2450,7 @@
         <x:v>來源限制</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>本期聚焦台灣與東南亞。CoWoS、美光、10 月 14 日工廠 AI 合作及越南 10 月 3 日 FDI 資料明列為追蹤或背景。展示規格、公司目標、園區估算與 GDP 預測均非已完成訂單。友達與馬來西亞園區數字依具名採訪；胡志明市電價缺原始會議文件及最終費率，越南製造業及資金來源分項未核對官方原表，這些部分屬來源受限。營運影響與情境推演為編輯分析，未披露的訂單、基期與影響金額保持未知。 活動地點依主辦資料補充；MSRD 招募起日存在 10/14 與 10/15 兩種主辦頁記載，KLCC 場館則一致。</x:v>
+        <x:v>本期聚焦台灣與東南亞。CoWoS、美光、10 月 14 日工廠 AI 合作及越南 10 月 3 日 FDI 資料明列為追蹤或背景。展示規格、公司目標、園區估算與 GDP 預測均非已完成訂單。友達與馬來西亞園區數字依具名採訪；胡志明市電價缺原始會議文件及最終費率，越南製造業及資金來源分項未核對官方原表，這些部分屬來源受限。未披露的訂單、基期與影響金額保持未知。 活動地點依主辦資料補充；MSRD 招募起日存在 10/14 與 10/15 兩種主辦頁記載，KLCC 場館則一致。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -2548,13 +2466,13 @@
         <x:v>資料更新</x:v>
       </x:c>
       <x:c r="B16" s="11" t="d">
-        <x:v>2026-10-17T11:34:06.828Z</x:v>
+        <x:v>2026-10-17T11:53:49.157Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95ec172c6d644ddd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd79b98bf8c6b47cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,12 +38,6 @@
       <b val="1"/>
       <color rgb="001F6B56"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="PingFang TC"/>
-      <color rgb="001F6B56"/>
-      <sz val="11"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="4">
@@ -86,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -98,17 +92,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,12 +464,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="88" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -494,7 +481,6 @@
     <row r="2" ht="6" customHeight="1">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -532,11 +518,6 @@
           </r>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="78" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -574,13 +555,8 @@
           </r>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1">
+    </row>
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>03</t>
@@ -616,19 +592,14 @@
           </r>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -658,19 +629,14 @@
           </r>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -700,19 +666,14 @@
           </r>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -742,19 +703,14 @@
           </r>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -784,19 +740,14 @@
           </r>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -826,19 +777,14 @@
           </r>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -868,19 +814,14 @@
           </r>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -908,30 +849,13 @@
             </rPr>
             <t>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。</t>
           </r>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>開啟 ›</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="重點" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要版" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整版" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'重點'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'摘要版'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'完整版'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -859,4 +861,408 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007A8780"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-17 日報重點</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="206" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>本週追蹤：台積電 CoWoS 量產與美光台中 HBM 封裝測試廠啟用</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>台積電 10 月 15 日法說表示，5 倍光罩尺寸的 CoWoS 已量產；同日美光台中 AATT2 先進封裝測試廠開幕，支援 HBM。這兩項是本週進展，今日整合追蹤，並無新增產能數字。地點：美光啟用典禮：台灣台中，美光先進封裝測試二廠（AATT2）。AI 設計需求先進入晶圓製造，再由封裝整合邏輯晶片與 HBM，經測試後交給伺服器廠。晶圓、記憶體及封裝任一環節的良率或交期，都可能限制最終交付；各廠擴產公告不能直接相加成可用系統。HBM 連結加速器封裝，伺服器 DRAM 連結系統記憶體，NAND 與企業 SSD 則連結儲存。TrendForce 9 月 30 日研究描述伺服器與企業 SSD 需求較強、消費端採購審慎，屬背景與預測，不能推成所有記憶體供應商同步增加獲利。前段要看蝕刻、沉積與設備電源，後段要看基板、接合、探針、燒機及可靠度。TrendForce 10 月 13 日列出台灣的 MPI、WinWay、Chroma 與 ASE 等測試或封裝角色；這是產業角色圖，未證實它們取得本案新訂單。AATT2 新增 HBM 產出、設備訂單及個別供應商營收未披露。台積電第三季美元營收 467.2 億美元，毛利率 66.4%；新台幣營收約 1.494 兆元、年增 50.9%，淨利 7,630.6 億元、年增 68.7%。不同貨幣成長率不可混用，這些是 10 月 15 日公布的公司實績。晶圓到後段交付：CoWoS / HBM。查證信心：高。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="206" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>台廠於聖荷西 OCP 展示整機櫃、800 VDC 電源與液冷</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>中央社 10 月 17 日整理 10 月 12 至 15 日於美國加州聖荷西舉辦的 OCP 展會：緯穎、華碩與勤誠等展示下一代伺服器或機櫃，台達電、光寶與康舒展示高壓直流電源及相關方案。台達電 10 月 15 日公司稿列出 800 VDC 電源櫃、備援與液冷產品，展示規格仍需與量產部署分開。地點：美國加州聖荷西，San Jose McEnery Convention Center。OCP Global Summit 2026 於當地時間 10 月 12 至 15 日在美國加州聖荷西舉行，主場館為 San Jose McEnery Convention Center。本文追蹤台灣參展供應鏈；展會位於美國，不代表文中所有廠商的生產或投資地都在美國。晶片、HBM 與封裝完成後，仍需主機板、網路、機構、電源、備援、冷卻與整機測試。系統可用率及現場供電會影響客戶何時驗收；高算力規格只能回答其中一段。台達電、光寶與康舒的展示，讓高壓直流電源設計與整機整合成為可比較項目。本期未取得各廠同規格成本、效率曲線與量產訂單，無法判定市占變化；產品規格與客戶認證需要分開比較。台達電列出 660 kW 電源櫃及 480 kW 備援規格，代表產品額定能力，不能當成每個客戶實際用電或已售出的容量。800 V 是架構電壓，也不等於節電百分比。同口徑售價、成本、客戶訂單及實際部署量未披露。展示的供電架構：800 VDC。查證信心：高。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="142" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>胡志明市要求釐清 AI 資料中心電價，投資模型面臨費率認定</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>TNGlobal 10 月 16 日報導，胡志明市工業區管理機關在 10 月 15 日經濟會議要求統一 AI 資料中心電價指引。所涉 AIC 與 KBC 計畫早於 3 月公布，總規劃金額 21 億美元；本次新增進展是電價問題，並非新宣布投資。地點：越南胡志明市；專案位於新富中工業區（Tan Phu Trung Industrial Park）。爭點是適用商業或製造業電價。較高電價可能改變營運成本、財務可行性及進度；本期沒有已定案費率、用電曲線或投資報酬模型，無法估算確切成本差額。原始會議文件、最終費率、用電曲線與電力合約未取得。TNGlobal 報導所列首期規劃最高 50 MW，而 21 億美元是既有計畫的總投資描述；兩者時程與範圍未完整對齊。本期不以總金額除以首期容量估算每 MW 造價，也不把規劃容量當成已通電或已出租容量。既有資料中心計畫金額：US$2.1B。查證信心：中。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="126" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>背景追蹤：NVIDIA 公布半導體檢測、測試與工廠 AI 合作</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>NVIDIA 10 月 14 日公司稿列出 KLA 檢測、Advantest 測試，以及鴻海、FANUC 等工廠 AI 合作。本期把它作為台灣供應鏈與終端工廠的背景追蹤；各場域地點、全面量產時程與全廠投資報酬未完整公開。地點：全球合作發布；各工廠實際導入地點未完整披露。晶片及伺服器提供算力，檢測與測試設備產生資料，工廠再把模型接到工程、排程或現場流程。合作名單提供可能的整合介面，尚不足以證明所有設備已串接，或同一套方法可複製到每座工廠。具名部署廠址、合約計價與量化全廠收益未完整公開。觀察導入進度，尚無可核對的全廠收益：試點與驗收。查證信心：中。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="174" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>馬來西亞半導體招募涵蓋製程、設備與廠務，人才連結台灣供應鏈</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>中央社 10 月 16 日報導，雪蘭莪相關機構在吉隆坡會展中心（KLCC）主辦的半導體招募活動提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備及廠務。官員表示兩座 IC 設計園區有 20 家公司、409 名工程師，與檳城製造、組裝測試形成互補。地點：馬來西亞吉隆坡，吉隆坡會展中心（KLCC）；由雪蘭莪相關機構主辦。招募活動場館為馬來西亞吉隆坡的吉隆坡會展中心（KLCC），不是把主辦單位「雪蘭莪」當成城市。Sidec 與中央社資料列 10 月 14 至 17 日，ASEM 招募專頁則列 10 月 15 至 17 日；地點一致，但子活動起日有差異，本期保留此限制。後段製造要靠製程、測試、設備維修與廠務共同運作，設計聚落也需要客戶及製造端協作。職缺提供需求線索，不能直接當成新增就業、產能或已支付薪資。實際聘用與留任未披露；園區及計畫數字依官員陳述。中央社引述官員表示，雪蘭莪將與檳城及國民投資機構參與總值馬幣 1.5 億令吉的計畫。來源未列本期撥款、外資占比或到位時程；此金額為合作計畫規模，與新增 FDI 統計口徑不同。活動提供的職缺，並非已聘人數：&gt;1,500。查證信心：中。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="126" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>友達布局玻璃基板與光通訊零組件，2030 年純面板占比目標為 30%</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>友達董事長彭双浪 10 月 17 日表示，公司在先進封裝將扮演零組件供應者，運用玻璃與 TGV 技術；與康寧合作的技術已有低軌衛星天線應用。MicroLED 光通訊與 CPO 的量產時間估計仍為兩至三年，屬公司展望。玻璃加工能力可延伸到不同零組件，但封裝用玻璃的可靠度、平整度與量產良率仍需客戶驗證。低軌衛星應用已有進展，不能直接當成半導體封裝已通過認證。30% 是 2030 年純面板營收占比目標，並非營收下跌 30%。本期依中央社具名採訪，未取得逐字稿、客戶認證或新業務獲利資料，標為來源受限。純面板營收占比目標：2030 / 30%。查證信心：中。新業務獲利、客戶認證及完整逐字稿尚未取得。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>RTX Spark 電腦 10 月 16 日上市，台灣設計、封裝與品牌串接終端 AI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>NVIDIA 10 月 16 日宣布 RTX Spark Windows 電腦上市，品牌包括華碩、微星及多家國際 PC 廠，採 Grace CPU 與 Blackwell GPU。公司主管向中央社說明聯發科參與 CPU 設計，並使用 CoWoS 封裝；需求與產能判斷仍屬公司說法。NVIDIA 發布資料列出 Grace CPU、Blackwell GPU 及華碩、微星等品牌。公司主管向中央社表示，聯發科參與 CPU 設計，平台採 CoWoS 封裝；本期未核實 HBM 用量。本期未取得出貨、使用率及完整生命週期成本。公司公布的最高統一記憶體規格：128 GB。查證信心：高。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="126" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>經濟部說明赴美園區由業者籌資，每座估 20 億至 40 億美元</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>經濟部 10 月 16 日向中央社說明，將與電電公會推動海外產業園區，採業者出資、政府協助模式。龔明鑫專訪提及由德州起步、規劃不只一座；單一園區 20 億至 40 億美元是估算，土地取得細節尚未對外確認。地點：投資規劃：美國德州；具體園區用地仍待確認。經濟部說明由業者出資、政府協助，並與電電公會推動海外產業園區。規劃從德州起步、不只一座，單一園區估算為 20 億至 40 億美元。金額來自部長專訪與經濟部對媒體說明，尚未取得完整融資、預算或土地契約文件。不能當成政府已編列支出，或業者已全數承諾的資本。開發主體、用地、完整融資及入駐名單尚未確認。每座園區的規劃估算：US$2–4B。查證信心：中。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="126" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>中經院上修台灣全年成長預測至 12.16%，需分開看實績與展望</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>中經院 10 月 16 日公布第四季預測，把 2026 年經濟成長率由 7 月的 10.35% 上修至 12.16%，提高 1.81 個百分點。預估內需貢獻 6.63 個百分點、國外淨需求貢獻 5.53 個百分點；全年數字仍是預測。10.35% 與 12.16% 是同一年度在不同時間的預測，差額為 1.81 個百分點。第四季預估年增 8.20%，面對去年同期高基期；增速放緩本身不代表當季產出縮減。中經院把 AI 需求、企業擴產與國內投資列為預測動能，並列出融資、地緣政治與 AI 資安等不確定性。這些是研究機構對全年表現的預測依據。全年 GDP 尚為預測，後續實績可能修訂。中經院 2026 年全年 GDP 成長預測：12.16%。查證信心：高。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="158" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t>區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="007A8780"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">   10/17
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。地點：越南全國統計；非單一活動或工廠。註冊額包括新案、增資與股權交易，實現額是不同口徑，不能相加。兩者也未對應同一批投資案，不能以 210.7 除以 503.6 當成本期計畫完成率；本期來源未列可比基期金額。製造業及資金來源分項未核對官方原表；實現額屬估計。VnEconomy 10 月 4 日轉述，新案與增資合計中，製造加工業為 218.2 億美元、占 50.3%；新加坡則是新註冊外資最大來源，金額 92.6 億美元、占 31.7%。前者分母是新案加增資，後者是新註冊資本，均不能套用到 503.6 億美元總註冊額。這些分項尚未核對官方原始明細表，屬來源受限。前三季 FDI 實現額年增：12.1% YoY。查證信心：中：總量有官方來源，新增分項待核對原表。</t>
+          </r>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -20,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="m/d"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +41,20 @@
     <font>
       <name val="PingFang TC"/>
       <b val="1"/>
+      <color rgb="007A8780"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="PingFang TC"/>
+      <b val="1"/>
       <color rgb="001F6B56"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="PingFang TC"/>
+      <b val="1"/>
+      <color rgb="003B4A44"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -82,23 +97,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,11 +492,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -480,34 +507,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="6" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="62" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>新聞</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>事件日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="66" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>本週追蹤：台積電 CoWoS 量產與美光台中 HBM 封裝測試廠啟用</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">本週追蹤：台積電 CoWoS 量產與美光台中 HBM 封裝測試廠啟用
 </t>
           </r>
           <r>
@@ -520,31 +552,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="4" ht="78" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="C3" s="6" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="4" ht="82" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>台廠於聖荷西 OCP 展示整機櫃、800 VDC 電源與液冷</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">台廠於聖荷西 OCP 展示整機櫃、800 VDC 電源與液冷
 </t>
           </r>
           <r>
@@ -557,31 +584,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="C4" s="6" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="5" ht="82" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>胡志明市要求釐清 AI 資料中心電價，投資模型面臨費率認定</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">胡志明市要求釐清 AI 資料中心電價，投資模型面臨費率認定
 </t>
           </r>
           <r>
@@ -594,31 +616,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="C5" s="6" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>背景追蹤：NVIDIA 公布半導體檢測、測試與工廠 AI 合作</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">背景追蹤：NVIDIA 公布半導體檢測、測試與工廠 AI 合作
 </t>
           </r>
           <r>
@@ -631,31 +648,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="C6" s="9" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="7" ht="82" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>馬來西亞半導體招募涵蓋製程、設備與廠務，人才連結台灣供應鏈</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞半導體招募涵蓋製程、設備與廠務，人才連結台灣供應鏈
 </t>
           </r>
           <r>
@@ -668,31 +680,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="C7" s="9" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>友達布局玻璃基板與光通訊零組件，2030 年純面板占比目標為 30%</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">友達布局玻璃基板與光通訊零組件，2030 年純面板占比目標為 30%
 </t>
           </r>
           <r>
@@ -705,31 +712,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="C8" s="9" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="9" ht="82" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>RTX Spark 電腦 10 月 16 日上市，台灣設計、封裝與品牌串接終端 AI</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">RTX Spark 電腦 10 月 16 日上市，台灣設計、封裝與品牌串接終端 AI
 </t>
           </r>
           <r>
@@ -742,31 +744,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="C9" s="9" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>經濟部說明赴美園區由業者籌資，每座估 20 億至 40 億美元</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">經濟部說明赴美園區由業者籌資，每座估 20 億至 40 億美元
 </t>
           </r>
           <r>
@@ -779,31 +776,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="C10" s="9" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>中經院上修台灣全年成長預測至 12.16%，需分開看實績與展望</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">中經院上修台灣全年成長預測至 12.16%，需分開看實績與展望
 </t>
           </r>
           <r>
@@ -816,31 +808,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="C11" s="9" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="12" ht="82" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開
 </t>
           </r>
           <r>
@@ -852,11 +839,14 @@
             <t>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。</t>
           </r>
         </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>46298</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
@@ -870,11 +860,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -884,34 +875,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="6" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="206" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>新聞</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>事件日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="210" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>本週追蹤：台積電 CoWoS 量產與美光台中 HBM 封裝測試廠啟用</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">本週追蹤：台積電 CoWoS 量產與美光台中 HBM 封裝測試廠啟用
 </t>
           </r>
           <r>
@@ -924,31 +920,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="4" ht="206" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="C3" s="6" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="4" ht="210" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>台廠於聖荷西 OCP 展示整機櫃、800 VDC 電源與液冷</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">台廠於聖荷西 OCP 展示整機櫃、800 VDC 電源與液冷
 </t>
           </r>
           <r>
@@ -961,31 +952,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="5" ht="142" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="C4" s="6" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="5" ht="162" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>胡志明市要求釐清 AI 資料中心電價，投資模型面臨費率認定</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">胡志明市要求釐清 AI 資料中心電價，投資模型面臨費率認定
 </t>
           </r>
           <r>
@@ -998,31 +984,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="6" ht="126" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="C5" s="6" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>背景追蹤：NVIDIA 公布半導體檢測、測試與工廠 AI 合作</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">背景追蹤：NVIDIA 公布半導體檢測、測試與工廠 AI 合作
 </t>
           </r>
           <r>
@@ -1035,31 +1016,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="7" ht="174" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="C6" s="9" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="7" ht="194" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>馬來西亞半導體招募涵蓋製程、設備與廠務，人才連結台灣供應鏈</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞半導體招募涵蓋製程、設備與廠務，人才連結台灣供應鏈
 </t>
           </r>
           <r>
@@ -1072,31 +1048,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="8" ht="126" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="C7" s="9" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="8" ht="130" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>友達布局玻璃基板與光通訊零組件，2030 年純面板占比目標為 30%</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">友達布局玻璃基板與光通訊零組件，2030 年純面板占比目標為 30%
 </t>
           </r>
           <r>
@@ -1109,31 +1080,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="9" ht="110" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="C8" s="9" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="9" ht="114" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>RTX Spark 電腦 10 月 16 日上市，台灣設計、封裝與品牌串接終端 AI</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">RTX Spark 電腦 10 月 16 日上市，台灣設計、封裝與品牌串接終端 AI
 </t>
           </r>
           <r>
@@ -1146,31 +1112,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="10" ht="126" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="C9" s="9" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="10" ht="130" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>經濟部說明赴美園區由業者籌資，每座估 20 億至 40 億美元</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">經濟部說明赴美園區由業者籌資，每座估 20 億至 40 億美元
 </t>
           </r>
           <r>
@@ -1183,31 +1144,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="11" ht="126" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="C10" s="9" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>中經院上修台灣全年成長預測至 12.16%，需分開看實績與展望</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">中經院上修台灣全年成長預測至 12.16%，需分開看實績與展望
 </t>
           </r>
           <r>
@@ -1220,31 +1176,26 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="12" ht="158" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="C11" s="9" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="12" ht="178" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t>區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="007A8780"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">   10/17
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開
 </t>
           </r>
           <r>
@@ -1256,11 +1207,14 @@
             <t>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。地點：越南全國統計；非單一活動或工廠。註冊額包括新案、增資與股權交易，實現額是不同口徑，不能相加。兩者也未對應同一批投資案，不能以 210.7 除以 503.6 當成本期計畫完成率；本期來源未列可比基期金額。製造業及資金來源分項未核對官方原表；實現額屬估計。VnEconomy 10 月 4 日轉述，新案與增資合計中，製造加工業為 218.2 億美元、占 50.3%；新加坡則是新註冊外資最大來源，金額 92.6 億美元、占 31.7%。前者分母是新案加增資，後者是新註冊資本，均不能套用到 503.6 億美元總註冊額。這些分項尚未核對官方原始明細表，屬來源受限。前三季 FDI 實現額年增：12.1% YoY。查證信心：中：總量有官方來源，新增分項待核對原表。</t>
           </r>
         </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>46298</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="m/d"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +56,13 @@
       <color rgb="003B4A44"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="PingFang TC"/>
+      <color rgb="003B4A44"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -125,6 +135,9 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -860,18 +873,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="86" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-17 日報重點</t>
+          <t>2026-10-17 日報完整版</t>
         </is>
       </c>
     </row>
@@ -891,6 +905,11 @@
           <t>事件日期</t>
         </is>
       </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>CEO 觀點（AI 分析，非事實）</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="210" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -923,6 +942,11 @@
       <c r="C3" s="6" t="n">
         <v>46310</v>
       </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>台積電 CoWoS 量產與美光 HBM 封測廠啟用，代表蝕刻、沉積等前段製程與先進封裝的電漿與射頻電源需求仍在延續。CEO 會追問台灣客戶的設備交機排程是否跟上這些產能、哪些製程需要更高精度的功率控制，以及在台服務與備品是否足以支援新廠爬坡。新增產出未披露，應以客戶實際下單與交機時程驗證，不宜直接推估營收。</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="210" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -955,6 +979,11 @@
       <c r="C4" s="6" t="n">
         <v>46310</v>
       </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>800 VDC 機櫃供電與液冷成為台廠展示重點，顯示資料中心電源架構正朝高壓直流發展。對電源轉換廠商而言，關鍵在轉換效率、功率密度與認證時程，以及與台達、光寶等台灣電源廠是競爭還是合作。CEO 會檢視產品藍圖是否涵蓋 800 V 架構、是否需要與 ODM 及雲端客戶共同驗證；展示不等於量產訂單，仍需追蹤實際部署。</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="162" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -987,6 +1016,11 @@
       <c r="C5" s="6" t="n">
         <v>46310</v>
       </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>胡志明市資料中心電價尚未定案，會影響當地 AI 資料中心的成本與時程。電價越高，客戶越重視電源轉換效率與能源管理，這是高效率電源產品的賣點；但專案規模與時程仍不確定，CEO 會把越南列為觀察市場，等電價與首期 50 MW 時程明朗後再投入資源。</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1019,6 +1053,11 @@
       <c r="C6" s="9" t="n">
         <v>46309</v>
       </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>NVIDIA 與 KLA、Advantest 等檢測、測試及工廠自動化業者合作，代表工廠 AI 需要大量設備資料與即時控制。對精密量測與控制儀器廠商而言，設備資料介面、可程式化與即時回饋能力可能成為新的產品要求；CEO 會評估自家產品能否提供這類資料、是否需要加入相關生態系，但目前部署與效益仍未完整公開。</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="194" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1051,6 +1090,11 @@
       <c r="C7" s="9" t="n">
         <v>46311</v>
       </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>馬來西亞積極招募設計、製程、設備與廠務人才，反映當地半導體後段與設計聚落持續擴張。對設備商而言，這代表當地客戶與裝機量可能增加，也意味工程與服務人才競爭更激烈。CEO 會檢視在馬來西亞的服務據點與人力布局，以及能否與當地大學和園區合作培訓。</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="130" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1083,6 +1127,11 @@
       <c r="C8" s="9" t="n">
         <v>46312</v>
       </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>面板廠跨入玻璃基板與 TGV 封裝零組件，先進封裝材料的供應來源可能增加。玻璃加工、雷射鑽孔與鍍膜同樣需要穩定的電漿與精密電源控制，CEO 可能把這類業者視為新的製程設備客群；但量產要等兩到三年，客戶認證也未確定，較適合先建立技術接觸並觀察驗證進度。</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="114" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -1115,6 +1164,11 @@
       <c r="C9" s="9" t="n">
         <v>46311</v>
       </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>終端 AI PC 上市主要牽動 PC 需求，與精密電源設備的直接關聯較低；間接影響在於 CoWoS 需求增加，帶動上游設備與電源。CEO 多半會把它視為 AI 需求從資料中心延伸到終端的訊號，持續觀察出貨量，而非立即調整策略。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="130" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1147,6 +1201,11 @@
       <c r="C10" s="9" t="n">
         <v>46311</v>
       </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>台灣廠商若在德州等地設立海外園區，美國在地的電子製造與設備需求可能增加，總部在美國的電源與量測設備商有機會就近服務台灣客戶的美國據點。不過目前只是規劃估算，用地、資金與進駐廠商都未確認；CEO 會先向既有台灣客戶確認其美國擴廠時程，再評估在地銷售與服務配置。</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="130" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1179,6 +1238,11 @@
       <c r="C11" s="9" t="n">
         <v>46311</v>
       </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>台灣全年成長預測上修至 12.16%，主要由 AI 需求與企業投資帶動，代表台灣客戶的資本支出環境仍偏強。CEO 會把它當作總體背景，搭配客戶個別擴產計畫、匯率與地緣風險一起判斷；預測仍可能修正，不宜單獨作為接單依據。</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="178" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -1211,12 +1275,17 @@
       <c r="C12" s="9" t="n">
         <v>46298</v>
       </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>越南前三季外資註冊額年增 76.4%、製造業約占一半，顯示供應鏈持續分散到東南亞；但實現額只年增 12.1%，落地速度慢於承諾。CEO 會追蹤其中哪些屬於半導體、電子與資料中心專案，並以實際建廠與設備採購時程判斷機會，而不是看註冊金額。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -823,38 +823,6 @@
       </c>
       <c r="C11" s="9" t="n">
         <v>46311</v>
-      </c>
-    </row>
-    <row r="12" ht="82" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>46298</v>
       </c>
     </row>
   </sheetData>
@@ -873,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1244,43 +1212,6 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="178" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">區域背景：越南前三季 FDI 實現額年增 12.1%，註冊額與落地須分開
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>越南政府新聞網 10 月 3 日公布的前三季資料顯示，FDI 實現額估 210.7 億美元、年增 12.1%，總註冊外資為 503.6 億美元、年增 76.4%。這是本期新增的區域背景，資料截至 9 月 30 日，並非 10 月 17 日的新統計。地點：越南全國統計；非單一活動或工廠。註冊額包括新案、增資與股權交易，實現額是不同口徑，不能相加。兩者也未對應同一批投資案，不能以 210.7 除以 503.6 當成本期計畫完成率；本期來源未列可比基期金額。製造業及資金來源分項未核對官方原表；實現額屬估計。VnEconomy 10 月 4 日轉述，新案與增資合計中，製造加工業為 218.2 億美元、占 50.3%；新加坡則是新註冊外資最大來源，金額 92.6 億美元、占 31.7%。前者分母是新案加增資，後者是新註冊資本，均不能套用到 503.6 億美元總註冊額。這些分項尚未核對官方原始明細表，屬來源受限。前三季 FDI 實現額年增：12.1% YoY。查證信心：中：總量有官方來源，新增分項待核對原表。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>46298</v>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>越南前三季外資註冊額年增 76.4%、製造業約占一半，顯示供應鏈持續分散到東南亞；但實現額只年增 12.1%，落地速度慢於承諾。CEO 會追蹤其中哪些屬於半導體、電子與資料中心專案，並以實際建廠與設備採購時程判斷機會，而不是看註冊金額。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -561,7 +561,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>台積電 10 月 15 日法說表示，5 倍光罩尺寸的 CoWoS 已量產；同日美光台中 AATT2 先進封裝測試廠開幕，支援 HBM。這兩項是本週進展，今日整合追蹤，並無新增產能數字。</t>
+            <t>台積電 10 月 15 日法說表示，5 倍光罩尺寸的 CoWoS 已進入量產；同一天，美光在台中啟用支援 HBM 的 AATT2 先進封裝測試廠。兩件事都是本週稍早的進展，雙方都未公布新增產能數字。</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>中央社 10 月 17 日整理 10 月 12 至 15 日於美國加州聖荷西舉辦的 OCP 展會：緯穎、華碩與勤誠等展示下一代伺服器或機櫃，台達電、光寶與康舒展示高壓直流電源及相關方案。台達電 10 月 15 日公司稿列出 800 VDC 電源櫃、備援與液冷產品，展示規格仍需與量產部署分開。</t>
+            <t>據中央社 10 月 17 日整理，OCP 全球高峰會 10 月 12 至 15 日在美國聖荷西舉行，台廠是展場主角之一：緯穎、華碩與勤誠展出新一代伺服器與機櫃，台達電、光寶與康舒則主打高壓直流電源。台達電 10 月 15 日發布的資料列出 800 VDC 電源櫃、備援與液冷產品，這些仍是展示規格，不等於已量產部署。</t>
           </r>
         </is>
       </c>
@@ -625,7 +625,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>TNGlobal 10 月 16 日報導，胡志明市工業區管理機關在 10 月 15 日經濟會議要求統一 AI 資料中心電價指引。所涉 AIC 與 KBC 計畫早於 3 月公布，總規劃金額 21 億美元；本次新增進展是電價問題，並非新宣布投資。</t>
+            <t>據 TNGlobal 10 月 16 日報導，胡志明市工業區管理機關在 10 月 15 日的經濟會議上，要求釐清並統一 AI 資料中心的電價適用規則。相關的 AIC 與 KBC 計畫早在 3 月就已公布，總投資規劃 21 億美元；這次的新進展是電價問題，而不是新的投資。</t>
           </r>
         </is>
       </c>
@@ -657,7 +657,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>NVIDIA 10 月 14 日公司稿列出 KLA 檢測、Advantest 測試，以及鴻海、FANUC 等工廠 AI 合作。本期把它作為台灣供應鏈與終端工廠的背景追蹤；各場域地點、全面量產時程與全廠投資報酬未完整公開。</t>
+            <t>NVIDIA 10 月 14 日發布的資料列出多項合作：KLA 的檢測、Advantest 的測試，以及鴻海、FANUC 等業者的工廠 AI 應用。這是本週稍早的發布，各工廠的導入地點、量產時程與整廠投資報酬都尚未完整公開。</t>
           </r>
         </is>
       </c>
@@ -689,7 +689,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>中央社 10 月 16 日報導，雪蘭莪相關機構在吉隆坡會展中心（KLCC）主辦的半導體招募活動提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備及廠務。官員表示兩座 IC 設計園區有 20 家公司、409 名工程師，與檳城製造、組裝測試形成互補。</t>
+            <t>中央社 10 月 16 日報導，雪蘭莪相關機構在吉隆坡會展中心（KLCC）舉辦半導體招募活動，提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備與廠務。官員表示，兩座 IC 設計園區已有 20 家公司、409 名工程師，可與檳城的製造與封裝測試形成互補。</t>
           </r>
         </is>
       </c>
@@ -721,7 +721,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>友達董事長彭双浪 10 月 17 日表示，公司在先進封裝將扮演零組件供應者，運用玻璃與 TGV 技術；與康寧合作的技術已有低軌衛星天線應用。MicroLED 光通訊與 CPO 的量產時間估計仍為兩至三年，屬公司展望。</t>
+            <t>友達董事長彭双浪 10 月 17 日接受中央社專訪表示，友達將以玻璃與 TGV（玻璃通孔）技術切入先進封裝零組件，與康寧合作的技術已用於低軌衛星天線。他也預估，MicroLED 光通訊與 CPO 約兩到三年後量產。</t>
           </r>
         </is>
       </c>
@@ -729,7 +729,7 @@
         <v>46312</v>
       </c>
     </row>
-    <row r="9" ht="82" customHeight="1">
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>07</t>
@@ -753,7 +753,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>NVIDIA 10 月 16 日宣布 RTX Spark Windows 電腦上市，品牌包括華碩、微星及多家國際 PC 廠，採 Grace CPU 與 Blackwell GPU。公司主管向中央社說明聯發科參與 CPU 設計，並使用 CoWoS 封裝；需求與產能判斷仍屬公司說法。</t>
+            <t>NVIDIA 10 月 16 日宣布 RTX Spark Windows 電腦上市，華碩、微星等品牌推出搭載 Grace CPU 與 Blackwell GPU 的機種。NVIDIA 主管向中央社表示，聯發科參與了 CPU 設計，平台並採用 CoWoS 封裝。</t>
           </r>
         </is>
       </c>
@@ -785,7 +785,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>經濟部 10 月 16 日向中央社說明，將與電電公會推動海外產業園區，採業者出資、政府協助模式。龔明鑫專訪提及由德州起步、規劃不只一座；單一園區 20 億至 40 億美元是估算，土地取得細節尚未對外確認。</t>
+            <t>經濟部 10 月 16 日向中央社說明，將與電電公會推動海外產業園區，由業者出資、政府協助。部長龔明鑫在專訪中表示，計畫從美國德州起步，規劃不只一座，單一園區估計需要 20 億至 40 億美元。</t>
           </r>
         </is>
       </c>
@@ -817,7 +817,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>中經院 10 月 16 日公布第四季預測，把 2026 年經濟成長率由 7 月的 10.35% 上修至 12.16%，提高 1.81 個百分點。預估內需貢獻 6.63 個百分點、國外淨需求貢獻 5.53 個百分點；全年數字仍是預測。</t>
+            <t>中經院 10 月 16 日公布最新預測，將台灣 2026 年經濟成長率從 7 月預估的 10.35% 上修至 12.16%，增加 1.81 個百分點。其中內需預估貢獻 6.63 個百分點，國外淨需求貢獻 5.53 個百分點。</t>
           </r>
         </is>
       </c>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>CEO 觀點（AI 分析，非事實）</t>
+          <t>AI 解讀</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>台積電 10 月 15 日法說表示，5 倍光罩尺寸的 CoWoS 已量產；同日美光台中 AATT2 先進封裝測試廠開幕，支援 HBM。這兩項是本週進展，今日整合追蹤，並無新增產能數字。地點：美光啟用典禮：台灣台中，美光先進封裝測試二廠（AATT2）。AI 設計需求先進入晶圓製造，再由封裝整合邏輯晶片與 HBM，經測試後交給伺服器廠。晶圓、記憶體及封裝任一環節的良率或交期，都可能限制最終交付；各廠擴產公告不能直接相加成可用系統。HBM 連結加速器封裝，伺服器 DRAM 連結系統記憶體，NAND 與企業 SSD 則連結儲存。TrendForce 9 月 30 日研究描述伺服器與企業 SSD 需求較強、消費端採購審慎，屬背景與預測，不能推成所有記憶體供應商同步增加獲利。前段要看蝕刻、沉積與設備電源，後段要看基板、接合、探針、燒機及可靠度。TrendForce 10 月 13 日列出台灣的 MPI、WinWay、Chroma 與 ASE 等測試或封裝角色；這是產業角色圖，未證實它們取得本案新訂單。AATT2 新增 HBM 產出、設備訂單及個別供應商營收未披露。台積電第三季美元營收 467.2 億美元，毛利率 66.4%；新台幣營收約 1.494 兆元、年增 50.9%，淨利 7,630.6 億元、年增 68.7%。不同貨幣成長率不可混用，這些是 10 月 15 日公布的公司實績。晶圓到後段交付：CoWoS / HBM。查證信心：高。</t>
+            <t>台積電 10 月 15 日法說表示，5 倍光罩尺寸的 CoWoS 已進入量產；同一天，美光在台中啟用支援 HBM 的 AATT2 先進封裝測試廠。兩件事都是本週稍早的進展，雙方都未公布新增產能數字。AI 晶片從晶圓製造出發，經過封裝與 HBM 整合、測試後，才交給伺服器廠組裝。因此任何一段的良率或交期卡住，都會限制最終出貨，各廠的擴產公告也不能直接加總成可用的系統數量。HBM 用於加速器封裝，伺服器 DRAM 用於系統記憶體，NAND 與企業 SSD 則用於儲存。TrendForce 9 月 30 日的研究指出，伺服器與企業 SSD 需求較強，消費端採購偏保守；這是研究機構的預測，不代表所有記憶體廠的獲利會同步成長。前段製程仰賴蝕刻、沉積與設備電源，後段則看基板、接合、探針、燒機與可靠度測試。TrendForce 10 月 13 日列出 MPI、WinWay、Chroma 與 ASE 等台灣廠商在測試與封裝的角色，不過這是產業分工圖，並未顯示它們因這兩件事取得新訂單。台積電同日公布第三季實績：美元營收 467.2 億美元、毛利率 66.4%；新台幣營收約 1.494 兆元、年增 50.9%，淨利 7,630.6 億元、年增 68.7%。美元與新台幣的成長率各自計算，不宜混用。美光 AATT2 新增的 HBM 產出、設備訂單，以及對個別供應商營收的影響都尚未公布。地點：台灣台中，美光先進封裝測試二廠（AATT2）。</t>
           </r>
         </is>
       </c>
@@ -916,7 +916,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="210" customHeight="1">
+    <row r="4" ht="178" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>02</t>
@@ -940,7 +940,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>中央社 10 月 17 日整理 10 月 12 至 15 日於美國加州聖荷西舉辦的 OCP 展會：緯穎、華碩與勤誠等展示下一代伺服器或機櫃，台達電、光寶與康舒展示高壓直流電源及相關方案。台達電 10 月 15 日公司稿列出 800 VDC 電源櫃、備援與液冷產品，展示規格仍需與量產部署分開。地點：美國加州聖荷西，San Jose McEnery Convention Center。OCP Global Summit 2026 於當地時間 10 月 12 至 15 日在美國加州聖荷西舉行，主場館為 San Jose McEnery Convention Center。本文追蹤台灣參展供應鏈；展會位於美國，不代表文中所有廠商的生產或投資地都在美國。晶片、HBM 與封裝完成後，仍需主機板、網路、機構、電源、備援、冷卻與整機測試。系統可用率及現場供電會影響客戶何時驗收；高算力規格只能回答其中一段。台達電、光寶與康舒的展示，讓高壓直流電源設計與整機整合成為可比較項目。本期未取得各廠同規格成本、效率曲線與量產訂單，無法判定市占變化；產品規格與客戶認證需要分開比較。台達電列出 660 kW 電源櫃及 480 kW 備援規格，代表產品額定能力，不能當成每個客戶實際用電或已售出的容量。800 V 是架構電壓，也不等於節電百分比。同口徑售價、成本、客戶訂單及實際部署量未披露。展示的供電架構：800 VDC。查證信心：高。</t>
+            <t>據中央社 10 月 17 日整理，OCP 全球高峰會 10 月 12 至 15 日在美國聖荷西舉行，台廠是展場主角之一：緯穎、華碩與勤誠展出新一代伺服器與機櫃，台達電、光寶與康舒則主打高壓直流電源。台達電 10 月 15 日發布的資料列出 800 VDC 電源櫃、備援與液冷產品，這些仍是展示規格，不等於已量產部署。晶片、HBM 與封裝完成後，還需要主機板、網路、機構件、電源、備援、冷卻與整機測試，才能變成可交付的機櫃。也因此，客戶何時驗收取決於系統可用率與機房供電，而不只是算力規格。台達電列出 660 kW 電源櫃與 480 kW 備援規格，這是產品的額定能力，並非客戶實際用電或已售出的容量；800 V 則是供電架構的電壓，不是節電比例。台達電、光寶與康舒同場展出，讓高壓直流電源有了比較基礎，但各廠同規格的成本、效率曲線與量產訂單都未公開，目前還看不出市占變化。同規格售價、成本、客戶訂單與實際部署量都尚未公開。地點：美國加州聖荷西，San Jose McEnery Convention Center。</t>
           </r>
         </is>
       </c>
@@ -953,7 +953,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="162" customHeight="1">
+    <row r="5" ht="146" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>03</t>
@@ -977,7 +977,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>TNGlobal 10 月 16 日報導，胡志明市工業區管理機關在 10 月 15 日經濟會議要求統一 AI 資料中心電價指引。所涉 AIC 與 KBC 計畫早於 3 月公布，總規劃金額 21 億美元；本次新增進展是電價問題，並非新宣布投資。地點：越南胡志明市；專案位於新富中工業區（Tan Phu Trung Industrial Park）。爭點是適用商業或製造業電價。較高電價可能改變營運成本、財務可行性及進度；本期沒有已定案費率、用電曲線或投資報酬模型，無法估算確切成本差額。原始會議文件、最終費率、用電曲線與電力合約未取得。TNGlobal 報導所列首期規劃最高 50 MW，而 21 億美元是既有計畫的總投資描述；兩者時程與範圍未完整對齊。本期不以總金額除以首期容量估算每 MW 造價，也不把規劃容量當成已通電或已出租容量。既有資料中心計畫金額：US$2.1B。查證信心：中。</t>
+            <t>據 TNGlobal 10 月 16 日報導，胡志明市工業區管理機關在 10 月 15 日的經濟會議上，要求釐清並統一 AI 資料中心的電價適用規則。相關的 AIC 與 KBC 計畫早在 3 月就已公布，總投資規劃 21 億美元；這次的新進展是電價問題，而不是新的投資。爭點在於資料中心該適用商業電價還是製造業電價。電價較高會推升營運成本，也可能影響財務可行性與建設進度；不過最終費率、用電曲線與財務模型都還沒公開，目前無法估算確切差額。TNGlobal 提到首期規劃最高 50 MW，而 21 億美元是整體計畫的投資規模，兩者的範圍與時程並不一致，不宜相除推算每 MW 造價；規劃容量也不等於已通電或已出租的容量。原始會議紀錄、最終電價、用電曲線與購電合約都尚未取得。地點：越南胡志明市，新富中工業區（Tan Phu Trung Industrial Park）。</t>
           </r>
         </is>
       </c>
@@ -990,7 +990,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="130" customHeight="1">
+    <row r="6" ht="114" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>04</t>
@@ -1014,7 +1014,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>NVIDIA 10 月 14 日公司稿列出 KLA 檢測、Advantest 測試，以及鴻海、FANUC 等工廠 AI 合作。本期把它作為台灣供應鏈與終端工廠的背景追蹤；各場域地點、全面量產時程與全廠投資報酬未完整公開。地點：全球合作發布；各工廠實際導入地點未完整披露。晶片及伺服器提供算力，檢測與測試設備產生資料，工廠再把模型接到工程、排程或現場流程。合作名單提供可能的整合介面，尚不足以證明所有設備已串接，或同一套方法可複製到每座工廠。具名部署廠址、合約計價與量化全廠收益未完整公開。觀察導入進度，尚無可核對的全廠收益：試點與驗收。查證信心：中。</t>
+            <t>NVIDIA 10 月 14 日發布的資料列出多項合作：KLA 的檢測、Advantest 的測試，以及鴻海、FANUC 等業者的工廠 AI 應用。這是本週稍早的發布，各工廠的導入地點、量產時程與整廠投資報酬都尚未完整公開。晶片與伺服器提供算力，檢測與測試設備產生資料，工廠再把模型接進工程、排程與現場作業。合作名單顯示可能的整合方式，但還不能證明所有設備都已串接，或同一套做法能複製到每座工廠。具名導入廠址、合約價格與可量化的整廠效益都尚未公開。</t>
           </r>
         </is>
       </c>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="194" customHeight="1">
+    <row r="7" ht="146" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>05</t>
@@ -1051,7 +1051,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>中央社 10 月 16 日報導，雪蘭莪相關機構在吉隆坡會展中心（KLCC）主辦的半導體招募活動提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備及廠務。官員表示兩座 IC 設計園區有 20 家公司、409 名工程師，與檳城製造、組裝測試形成互補。地點：馬來西亞吉隆坡，吉隆坡會展中心（KLCC）；由雪蘭莪相關機構主辦。招募活動場館為馬來西亞吉隆坡的吉隆坡會展中心（KLCC），不是把主辦單位「雪蘭莪」當成城市。Sidec 與中央社資料列 10 月 14 至 17 日，ASEM 招募專頁則列 10 月 15 至 17 日；地點一致，但子活動起日有差異，本期保留此限制。後段製造要靠製程、測試、設備維修與廠務共同運作，設計聚落也需要客戶及製造端協作。職缺提供需求線索，不能直接當成新增就業、產能或已支付薪資。實際聘用與留任未披露；園區及計畫數字依官員陳述。中央社引述官員表示，雪蘭莪將與檳城及國民投資機構參與總值馬幣 1.5 億令吉的計畫。來源未列本期撥款、外資占比或到位時程；此金額為合作計畫規模，與新增 FDI 統計口徑不同。活動提供的職缺，並非已聘人數：&gt;1,500。查證信心：中。</t>
+            <t>中央社 10 月 16 日報導，雪蘭莪相關機構在吉隆坡會展中心（KLCC）舉辦半導體招募活動，提供逾 1,500 個職缺，涵蓋設計、軟韌體、製程、設備與廠務。官員表示，兩座 IC 設計園區已有 20 家公司、409 名工程師，可與檳城的製造與封裝測試形成互補。後段製造需要製程、測試、設備維修與廠務人員一起運作，設計聚落也要有客戶與製造端配合。職缺數量反映招募需求，但不等於實際新增就業、產能或薪資支出。官員也提到，雪蘭莪將與檳城及國家投資機構合作推動規模 1.5 億令吉的計畫。來源未說明撥款時程與外資比例，這是合作計畫的規模，和 FDI 統計是不同的數字。實際聘用與留任人數尚未公布；各主辦頁面記載的活動起日為 10 月 14 日或 15 日，場館則一致。地點：馬來西亞吉隆坡，吉隆坡會展中心（KLCC）。</t>
           </r>
         </is>
       </c>
@@ -1088,7 +1088,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>友達董事長彭双浪 10 月 17 日表示，公司在先進封裝將扮演零組件供應者，運用玻璃與 TGV 技術；與康寧合作的技術已有低軌衛星天線應用。MicroLED 光通訊與 CPO 的量產時間估計仍為兩至三年，屬公司展望。玻璃加工能力可延伸到不同零組件，但封裝用玻璃的可靠度、平整度與量產良率仍需客戶驗證。低軌衛星應用已有進展，不能直接當成半導體封裝已通過認證。30% 是 2030 年純面板營收占比目標，並非營收下跌 30%。本期依中央社具名採訪，未取得逐字稿、客戶認證或新業務獲利資料，標為來源受限。純面板營收占比目標：2030 / 30%。查證信心：中。新業務獲利、客戶認證及完整逐字稿尚未取得。</t>
+            <t>友達董事長彭双浪 10 月 17 日接受中央社專訪表示，友達將以玻璃與 TGV（玻璃通孔）技術切入先進封裝零組件，與康寧合作的技術已用於低軌衛星天線。他也預估，MicroLED 光通訊與 CPO 約兩到三年後量產。面板廠的玻璃加工能力可以延伸到封裝零組件，但封裝用玻璃對可靠度、平整度與良率的要求更高，仍需通過客戶驗證；衛星天線的應用進展，也不代表已取得半導體封裝認證。報導中的 30% 是友達 2030 年純面板營收占比的目標，並不是營收下滑 30%。目前資訊來自具名專訪，尚未取得逐字稿、客戶認證進度與新業務的獲利資料。</t>
           </r>
         </is>
       </c>
@@ -1125,7 +1125,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>NVIDIA 10 月 16 日宣布 RTX Spark Windows 電腦上市，品牌包括華碩、微星及多家國際 PC 廠，採 Grace CPU 與 Blackwell GPU。公司主管向中央社說明聯發科參與 CPU 設計，並使用 CoWoS 封裝；需求與產能判斷仍屬公司說法。NVIDIA 發布資料列出 Grace CPU、Blackwell GPU 及華碩、微星等品牌。公司主管向中央社表示，聯發科參與 CPU 設計，平台採 CoWoS 封裝；本期未核實 HBM 用量。本期未取得出貨、使用率及完整生命週期成本。公司公布的最高統一記憶體規格：128 GB。查證信心：高。</t>
+            <t>NVIDIA 10 月 16 日宣布 RTX Spark Windows 電腦上市，華碩、微星等品牌推出搭載 Grace CPU 與 Blackwell GPU 的機種。NVIDIA 主管向中央社表示，聯發科參與了 CPU 設計，平台並採用 CoWoS 封裝。這款平台把台灣的晶片設計、先進封裝與 PC 品牌串在一起：聯發科參與 CPU 設計，平台採 CoWoS 封裝，華碩、微星等品牌推出終端產品。公司公布的最高統一記憶體規格為 128 GB；需求與產能的說法都來自 NVIDIA，HBM 用量也尚未證實。出貨量、使用率與完整生命週期成本都尚未公開。</t>
           </r>
         </is>
       </c>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="130" customHeight="1">
+    <row r="10" ht="114" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>08</t>
@@ -1162,7 +1162,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>經濟部 10 月 16 日向中央社說明，將與電電公會推動海外產業園區，採業者出資、政府協助模式。龔明鑫專訪提及由德州起步、規劃不只一座；單一園區 20 億至 40 億美元是估算，土地取得細節尚未對外確認。地點：投資規劃：美國德州；具體園區用地仍待確認。經濟部說明由業者出資、政府協助，並與電電公會推動海外產業園區。規劃從德州起步、不只一座，單一園區估算為 20 億至 40 億美元。金額來自部長專訪與經濟部對媒體說明，尚未取得完整融資、預算或土地契約文件。不能當成政府已編列支出，或業者已全數承諾的資本。開發主體、用地、完整融資及入駐名單尚未確認。每座園區的規劃估算：US$2–4B。查證信心：中。</t>
+            <t>經濟部 10 月 16 日向中央社說明，將與電電公會推動海外產業園區，由業者出資、政府協助。部長龔明鑫在專訪中表示，計畫從美國德州起步，規劃不只一座，單一園區估計需要 20 億至 40 億美元。20 億至 40 億美元來自部長與經濟部對媒體的說明，屬於規劃估算；目前沒有融資、預算或土地契約文件，因此既不是政府已編列的支出，也不是業者已承諾的投資。開發主體、園區用地、完整融資方式與進駐廠商名單都尚未確認。地點：美國德州（規劃中，具體用地待確認）。</t>
           </r>
         </is>
       </c>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="130" customHeight="1">
+    <row r="11" ht="114" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>09</t>
@@ -1199,7 +1199,7 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>中經院 10 月 16 日公布第四季預測，把 2026 年經濟成長率由 7 月的 10.35% 上修至 12.16%，提高 1.81 個百分點。預估內需貢獻 6.63 個百分點、國外淨需求貢獻 5.53 個百分點；全年數字仍是預測。10.35% 與 12.16% 是同一年度在不同時間的預測，差額為 1.81 個百分點。第四季預估年增 8.20%，面對去年同期高基期；增速放緩本身不代表當季產出縮減。中經院把 AI 需求、企業擴產與國內投資列為預測動能，並列出融資、地緣政治與 AI 資安等不確定性。這些是研究機構對全年表現的預測依據。全年 GDP 尚為預測，後續實績可能修訂。中經院 2026 年全年 GDP 成長預測：12.16%。查證信心：高。</t>
+            <t>中經院 10 月 16 日公布最新預測，將台灣 2026 年經濟成長率從 7 月預估的 10.35% 上修至 12.16%，增加 1.81 個百分點。其中內需預估貢獻 6.63 個百分點，國外淨需求貢獻 5.53 個百分點。中經院認為 AI 需求、企業擴產與國內投資是主要動能，同時提醒融資、地緣政治與 AI 資安等不確定因素。10.35% 與 12.16% 是同一年度在不同時間點的預測。第四季預估年增 8.20%，去年同期基期較高；增速放緩本身不代表當季產出減少。全年數字仍是預測，實際結果要等官方統計，屆時可能修正。</t>
           </r>
         </is>
       </c>

--- a/docs/exports/day-2026-10-17.xlsx
+++ b/docs/exports/day-2026-10-17.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>台積電 CoWoS 量產與美光 HBM 封測廠啟用，代表蝕刻、沉積等前段製程與先進封裝的電漿與射頻電源需求仍在延續。CEO 會追問台灣客戶的設備交機排程是否跟上這些產能、哪些製程需要更高精度的功率控制，以及在台服務與備品是否足以支援新廠爬坡。新增產出未披露，應以客戶實際下單與交機時程驗證，不宜直接推估營收。</t>
+          <t>台積電 CoWoS 量產與美光 HBM 封測廠啟用，代表蝕刻、沉積等前段製程與先進封裝的電漿與射頻電源需求仍在延續。值得追問的是：台灣客戶的設備交機排程是否跟上這些產能、哪些製程需要更高精度的功率控制，以及在台服務與備品是否足以支援新廠爬坡。新增產出尚未披露，較適合以客戶實際下單與交機時程驗證，不宜直接推估營收。</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>800 VDC 機櫃供電與液冷成為台廠展示重點，顯示資料中心電源架構正朝高壓直流發展。對電源轉換廠商而言，關鍵在轉換效率、功率密度與認證時程，以及與台達、光寶等台灣電源廠是競爭還是合作。CEO 會檢視產品藍圖是否涵蓋 800 V 架構、是否需要與 ODM 及雲端客戶共同驗證；展示不等於量產訂單，仍需追蹤實際部署。</t>
+          <t>800 VDC 機櫃供電與液冷成為台廠展示重點，顯示資料中心電源架構正朝高壓直流發展。對電源轉換業者而言，關鍵在轉換效率、功率密度與認證時程，以及與台達、光寶等台灣電源廠是競爭還是合作。可以檢視產品藍圖是否涵蓋 800 V 架構、是否需要與 ODM 及雲端客戶共同驗證；展示不等於量產訂單，仍需追蹤實際部署。</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>胡志明市資料中心電價尚未定案，會影響當地 AI 資料中心的成本與時程。電價越高，客戶越重視電源轉換效率與能源管理，這是高效率電源產品的賣點；但專案規模與時程仍不確定，CEO 會把越南列為觀察市場，等電價與首期 50 MW 時程明朗後再投入資源。</t>
+          <t>胡志明市資料中心電價尚未定案，會影響當地 AI 資料中心的成本與時程。電價越高，客戶越重視電源轉換效率與能源管理，這是高效率電源產品的賣點；但專案規模與時程仍不確定，越南較適合列為觀察市場，等電價與首期 50 MW 時程明朗後再投入資源。</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>NVIDIA 與 KLA、Advantest 等檢測、測試及工廠自動化業者合作，代表工廠 AI 需要大量設備資料與即時控制。對精密量測與控制儀器廠商而言，設備資料介面、可程式化與即時回饋能力可能成為新的產品要求；CEO 會評估自家產品能否提供這類資料、是否需要加入相關生態系，但目前部署與效益仍未完整公開。</t>
+          <t>NVIDIA 與 KLA、Advantest 等檢測、測試及工廠自動化業者合作，代表工廠 AI 需要大量設備資料與即時控制。對精密量測與控制儀器業者而言，設備資料介面、可程式化與即時回饋能力可能成為新的產品要求；可評估自家產品能否提供這類資料、是否需要加入相關生態系，但目前部署與效益仍未完整公開。</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>馬來西亞積極招募設計、製程、設備與廠務人才，反映當地半導體後段與設計聚落持續擴張。對設備商而言，這代表當地客戶與裝機量可能增加，也意味工程與服務人才競爭更激烈。CEO 會檢視在馬來西亞的服務據點與人力布局，以及能否與當地大學和園區合作培訓。</t>
+          <t>馬來西亞積極招募設計、製程、設備與廠務人才，反映當地半導體後段與設計聚落持續擴張。對設備商而言，這代表當地客戶與裝機量可能增加，也意味工程與服務人才競爭更激烈。值得檢視在馬來西亞的服務據點與人力布局，以及能否與當地大學和園區合作培訓。</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>面板廠跨入玻璃基板與 TGV 封裝零組件，先進封裝材料的供應來源可能增加。玻璃加工、雷射鑽孔與鍍膜同樣需要穩定的電漿與精密電源控制，CEO 可能把這類業者視為新的製程設備客群；但量產要等兩到三年，客戶認證也未確定，較適合先建立技術接觸並觀察驗證進度。</t>
+          <t>面板廠跨入玻璃基板與 TGV 封裝零組件，先進封裝材料的供應來源可能增加。玻璃加工、雷射鑽孔與鍍膜同樣需要穩定的電漿與精密電源控制，這類業者可能成為新的製程設備客群；但量產要等兩到三年，客戶認證也未確定，較適合先建立技術接觸並觀察驗證進度。</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>終端 AI PC 上市主要牽動 PC 需求，與精密電源設備的直接關聯較低；間接影響在於 CoWoS 需求增加，帶動上游設備與電源。CEO 多半會把它視為 AI 需求從資料中心延伸到終端的訊號，持續觀察出貨量，而非立即調整策略。</t>
+          <t>終端 AI PC 上市主要牽動 PC 需求，與精密電源設備的直接關聯較低；間接影響在於 CoWoS 需求增加，帶動上游設備與電源。比較適合把它視為 AI 需求從資料中心延伸到終端的訊號，持續觀察出貨量，而非據此調整策略。</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>台灣廠商若在德州等地設立海外園區，美國在地的電子製造與設備需求可能增加，總部在美國的電源與量測設備商有機會就近服務台灣客戶的美國據點。不過目前只是規劃估算，用地、資金與進駐廠商都未確認；CEO 會先向既有台灣客戶確認其美國擴廠時程，再評估在地銷售與服務配置。</t>
+          <t>台灣廠商若在德州等地設立海外園區，美國在地的電子製造與設備需求可能增加，總部在美國的電源與量測設備商有機會就近服務台灣客戶的美國據點。不過目前只是規劃估算，用地、資金與進駐廠商都未確認，宜先向既有台灣客戶確認其美國擴廠時程，再評估在地銷售與服務配置。</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>台灣全年成長預測上修至 12.16%，主要由 AI 需求與企業投資帶動，代表台灣客戶的資本支出環境仍偏強。CEO 會把它當作總體背景，搭配客戶個別擴產計畫、匯率與地緣風險一起判斷；預測仍可能修正，不宜單獨作為接單依據。</t>
+          <t>台灣全年成長預測上修至 12.16%，主要由 AI 需求與企業投資帶動，代表台灣客戶的資本支出環境仍偏強。這比較適合當作總體背景，搭配客戶個別擴產計畫、匯率與地緣風險一起判斷；預測仍可能修正，不宜單獨作為接單依據。</t>
         </is>
       </c>
     </row>
